--- a/results/job_matches_2026-06-09.xlsx
+++ b/results/job_matches_2026-06-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,25 +853,25 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data/ML Engineer (AWS)</t>
+          <t>API Integrations Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capnexus</t>
+          <t>Colorado Access</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, API Gateway, RDS, Azure</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Snowflake, SQL Server, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb618ea44d30c0e0</t>
+          <t>https://www.indeed.com/viewjob?jk=3dea7c38b1b46e2c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - PGIM Technology (Hybrid - Newark, NJ)</t>
+          <t>Senior Data/ML Engineer (AWS)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PGIM</t>
+          <t>Capnexus</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, API Gateway, RDS, Azure</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,19 +916,19 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7feca5e666659d5</t>
+          <t>https://www.indeed.com/viewjob?jk=bb618ea44d30c0e0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - PGIM Technology</t>
+          <t>Senior Data Engineer - PGIM Technology (Hybrid - Newark, NJ)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>PGIM</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ddb3e15556877d</t>
+          <t>https://www.indeed.com/viewjob?jk=b7feca5e666659d5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Analytics</t>
+          <t>Senior Data Engineer - PGIM Technology</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lovevery</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b019f71f6d426d97</t>
+          <t>https://www.indeed.com/viewjob?jk=42ddb3e15556877d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer</t>
+          <t>Senior Data Engineer, Analytics</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>Lovevery</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Dataflow, Scala, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d4021156adfe1b</t>
+          <t>https://www.indeed.com/viewjob?jk=b019f71f6d426d97</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering</t>
+          <t>Senior DevOps/Platform Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>JITSU</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,19 +1056,19 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06eee63ec8fb01b9</t>
+          <t>https://www.indeed.com/viewjob?jk=dc401e882f1b7d3b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior DevOps/Platform Engineer</t>
+          <t>Sr. Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JITSU</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Dataflow, Scala, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc401e882f1b7d3b</t>
+          <t>https://www.indeed.com/viewjob?jk=27d4021156adfe1b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Engineer, Investment Technology</t>
+          <t>Specialist Solutions Architect - Data Engineering</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, IAM, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,59 +1126,59 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e247743b45089523</t>
+          <t>https://www.indeed.com/viewjob?jk=06eee63ec8fb01b9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Full Stack Engineer</t>
+          <t>Senior Engineer, Investment Technology</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>L&amp;T Technology Services Ltd.</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Cloud Storage, Spark, Scala, MySQL, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, Athena, S3, IAM, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c4b06a84a76fe1</t>
+          <t>https://www.indeed.com/viewjob?jk=e247743b45089523</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Full Stack Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>L&amp;T Technology Services Ltd.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,17 +1186,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, S3, IAM, Cloud Storage, Spark, Scala, MySQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10ead8343cec4879</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c4b06a84a76fe1</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>DTN</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=162c2ab9f292809c</t>
+          <t>https://www.indeed.com/viewjob?jk=cb35c7b57058adb4</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7be54a20fbf4431</t>
+          <t>https://www.indeed.com/viewjob?jk=10ead8343cec4879</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, BigQuery, Cloud Storage, Scala, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6773c1c434a7ae57</t>
+          <t>https://www.indeed.com/viewjob?jk=162c2ab9f292809c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5232892f9a4a9b08</t>
+          <t>https://www.indeed.com/viewjob?jk=d7be54a20fbf4431</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, BigQuery, Cloud Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5b9e1941fe0d4ca</t>
+          <t>https://www.indeed.com/viewjob?jk=6773c1c434a7ae57</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior AI Operations Engineer</t>
+          <t>Senior Data Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd1103c64558f430</t>
+          <t>https://www.indeed.com/viewjob?jk=5232892f9a4a9b08</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Operations Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DTN</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb35c7b57058adb4</t>
+          <t>https://www.indeed.com/viewjob?jk=dd1103c64558f430</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior BI Data Engineer</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Soleo Health</t>
+          <t>HealthStream</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dedc6497a9161a47</t>
+          <t>https://www.indeed.com/viewjob?jk=c6929e10d2183d6c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior BI Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DTN</t>
+          <t>Soleo Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, ELT, CI/CD</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33d845a6e90fbede</t>
+          <t>https://www.indeed.com/viewjob?jk=dedc6497a9161a47</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Development Engineer (Core Engine)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>DTN</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e32c70852b2e7e9</t>
+          <t>https://www.indeed.com/viewjob?jk=33d845a6e90fbede</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f53654a42d5f44e</t>
+          <t>https://www.indeed.com/viewjob?jk=4e32c70852b2e7e9</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74408bc2ca90f29e</t>
+          <t>https://www.indeed.com/viewjob?jk=3f53654a42d5f44e</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfcd3234ed7c76b1</t>
+          <t>https://www.indeed.com/viewjob?jk=74408bc2ca90f29e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Development Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NIKSUN, Inc.</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fd5208875d3c1b2</t>
+          <t>https://www.indeed.com/viewjob?jk=cfcd3234ed7c76b1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Engineer 2: AI Agentic Platform (Hybrid - Seattle, WA)</t>
+          <t>Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Digital Consultants</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, SQS, ECS, Azure, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1a42d221dac8991</t>
+          <t>https://www.indeed.com/viewjob?jk=d5b05b32ba6e729a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CD&amp;A Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>NIKSUN, Inc.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6cb0aa04ee83dc1</t>
+          <t>https://www.indeed.com/viewjob?jk=0fd5208875d3c1b2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer – Python + React (Healthcare Domain)</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nova Web Technologies</t>
+          <t>SWBC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff5c44492f4137d0</t>
+          <t>https://www.indeed.com/viewjob?jk=075826e3e1704244</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DBX/PowerBI Developer</t>
+          <t>Senior Engineer 2: AI Agentic Platform (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Cloud Storage, Spark, Scala, Snowflake, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1532e72abbad0fcf</t>
+          <t>https://www.indeed.com/viewjob?jk=e1a42d221dac8991</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>CD&amp;A Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Spark, Snowflake, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline, Terraform</t>
+          <t>RDS, Azure, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f417fbf524598c0</t>
+          <t>https://www.indeed.com/viewjob?jk=f6cb0aa04ee83dc1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Azure Engineer (Associate)</t>
+          <t>Data Engineer – Python + React (Healthcare Domain)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Nova Web Technologies</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dbe236b626e4a53</t>
+          <t>https://www.indeed.com/viewjob?jk=ff5c44492f4137d0</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer (Advanced Threat Protection)</t>
+          <t>DBX/PowerBI Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Terraform, Git</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Cloud Storage, Spark, Scala, Snowflake, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2c3719c3e2ec42</t>
+          <t>https://www.indeed.com/viewjob?jk=1532e72abbad0fcf</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CNA Insurance</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, RDS, Spark, Snowflake, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947710ea68d4354a</t>
+          <t>https://www.indeed.com/viewjob?jk=1f417fbf524598c0</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>Azure Engineer (Associate)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Rise Collective</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, NoSQL</t>
+          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff3b252b91a197e5</t>
+          <t>https://www.indeed.com/viewjob?jk=9dbe236b626e4a53</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior SQL Developer</t>
+          <t>Sr Cloud Infrastructure Engineer (Advanced Threat Protection)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
+          <t>AWS, GCP, BigQuery, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b418f223555b73b9</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2c3719c3e2ec42</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,14 +2106,14 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707d30063b198a61</t>
+          <t>https://www.indeed.com/viewjob?jk=3be9e819ada5cf6a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SQL Platform Engineer</t>
+          <t>Senior SQL Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e965a90207e77c</t>
+          <t>https://www.indeed.com/viewjob?jk=b418f223555b73b9</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Crumbl Cookies Franchises</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c53bb7a7aa686c9</t>
+          <t>https://www.indeed.com/viewjob?jk=707d30063b198a61</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineering Senior Advisor- Hybrid</t>
+          <t>SQL Platform Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Spark Streaming, Kafka, Oracle, MongoDB, NoSQL, Splunk, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ab95bf144a98568</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e965a90207e77c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineering Senior Advisor- Hybrid</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>CNA Insurance</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Spark Streaming, Kafka, Oracle, MongoDB, NoSQL, Splunk, CI/CD</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceca754c6b6fbfd5</t>
+          <t>https://www.indeed.com/viewjob?jk=947710ea68d4354a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Rise Collective</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55da546db249541e</t>
+          <t>https://www.indeed.com/viewjob?jk=ff3b252b91a197e5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer, IT Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Crumbl Cookies Franchises</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cde05fe8d78b7bea</t>
+          <t>https://www.indeed.com/viewjob?jk=60db0ac4d21d1076</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (.NET )</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Crumbl Cookies Franchises</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8fae101fea70214</t>
+          <t>https://www.indeed.com/viewjob?jk=4c53bb7a7aa686c9</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Blockchain Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=678a055b3ce18049</t>
+          <t>https://www.indeed.com/viewjob?jk=55da546db249541e</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr Associate Engineer, IT Software</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92370ed8cefd2963</t>
+          <t>https://www.indeed.com/viewjob?jk=cde05fe8d78b7bea</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Software Engineer (.NET )</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be9e819ada5cf6a</t>
+          <t>https://www.indeed.com/viewjob?jk=a8fae101fea70214</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Blockchain Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Crumbl Cookies Franchises</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60db0ac4d21d1076</t>
+          <t>https://www.indeed.com/viewjob?jk=678a055b3ce18049</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Software Engineering Senior Advisor- Hybrid</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, Spark Streaming, Kafka, Oracle, MongoDB, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b9a027a38e2401</t>
+          <t>https://www.indeed.com/viewjob?jk=1ab95bf144a98568</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineering Senior Advisor- Hybrid</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Spurs Sports &amp; Entertainment</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Spark, Spark Streaming, Kafka, Oracle, MongoDB, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31a3c71dc92d0e0c</t>
+          <t>https://www.indeed.com/viewjob?jk=ceca754c6b6fbfd5</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer, Go to Market (Remote)</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27f893425f230116</t>
+          <t>https://www.indeed.com/viewjob?jk=e5abed50f2367d51</t>
         </is>
       </c>
     </row>
@@ -2608,47 +2608,47 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Metronet</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8988ab1d912fc2fc</t>
+          <t>https://www.indeed.com/viewjob?jk=92370ed8cefd2963</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Offchain Labs</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, CodeBuild, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a00c080490fe5a6</t>
+          <t>https://www.indeed.com/viewjob?jk=18b9a027a38e2401</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>Spurs Sports &amp; Entertainment</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2de73d2117d18151</t>
+          <t>https://www.indeed.com/viewjob?jk=31a3c71dc92d0e0c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Frontend Software Engineer</t>
+          <t>Data Engineer, Go to Market (Remote)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Dresser Utility Solutions</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e77c6f0d763f738</t>
+          <t>https://www.indeed.com/viewjob?jk=27f893425f230116</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>IQVIA</t>
+          <t>Metronet</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Hive, Spark, PySpark, Scala, ETL, ELT, Terraform</t>
+          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=409022a27d0ec067</t>
+          <t>https://www.indeed.com/viewjob?jk=8988ab1d912fc2fc</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Offchain Labs</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Redford, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, CodeBuild, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29332168c78c58c</t>
+          <t>https://www.indeed.com/viewjob?jk=8a00c080490fe5a6</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d23e98febb4af71d</t>
+          <t>https://www.indeed.com/viewjob?jk=2de73d2117d18151</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Frontend Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Snooze an AM Eatery</t>
+          <t>Dresser Utility Solutions</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65eaed35b3d68901</t>
+          <t>https://www.indeed.com/viewjob?jk=2e77c6f0d763f738</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Junior Data Engineer (Faculty Specialist)</t>
+          <t>Software Engineer II, Wayfair Sponsored Shops</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>University of Maryland University College</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>College Park, MD, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Hive, Spark, SQL Server, PostgreSQL, Cassandra, ETL, Git</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaedc5d1808c1ed5</t>
+          <t>https://www.indeed.com/viewjob?jk=1700b3ad8a2acabe</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platforms &amp; Monetization</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Wowza Media Systems</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, MySQL, Data Modeling, ETL, REST API integration, Terraform</t>
+          <t>AWS, Glue, EMR, Hive, Spark, PySpark, Scala, ETL, ELT, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa5b3c703b2170b9</t>
+          <t>https://www.indeed.com/viewjob?jk=409022a27d0ec067</t>
         </is>
       </c>
     </row>
@@ -2988,17 +2988,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Redford, MI, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, Docker</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=953100d783ca43ac</t>
+          <t>https://www.indeed.com/viewjob?jk=c29332168c78c58c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72b083a5bbeb1232</t>
+          <t>https://www.indeed.com/viewjob?jk=d23e98febb4af71d</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>Snooze an AM Eatery</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35918117efc7ec73</t>
+          <t>https://www.indeed.com/viewjob?jk=65eaed35b3d68901</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Engineer, AI/ML Software</t>
+          <t>Junior Data Engineer (Faculty Specialist)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Analog Devices</t>
+          <t>University of Maryland University College</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>College Park, MD, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, GCP, Hadoop, Hive, Spark, SQL Server, PostgreSQL, Cassandra, ETL, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=664a13900407cad4</t>
+          <t>https://www.indeed.com/viewjob?jk=aaedc5d1808c1ed5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Architect 3 (Data Analyst 3)</t>
+          <t>Senior Software Engineer, Data Platforms &amp; Monetization</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>University of Connecticut</t>
+          <t>Wowza Media Systems</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Storrs, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, ETL, Pentaho, Power BI, Airflow, Python, SQL</t>
+          <t>AWS, Glue, Lambda, S3, RDS, MySQL, Data Modeling, ETL, REST API integration, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b2f300a70f64192</t>
+          <t>https://www.indeed.com/viewjob?jk=aa5b3c703b2170b9</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior System Software Engineer - DevOps and Infrastructure Automation</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c72aec67782f8030</t>
+          <t>https://www.indeed.com/viewjob?jk=953100d783ca43ac</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Lakebase Sales Specialist-Manufacturing</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50ab1973f17e0989</t>
+          <t>https://www.indeed.com/viewjob?jk=72b083a5bbeb1232</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sales Operations - Business Intelligence Engineer II</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>The Carlyle Group</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,29 +3251,29 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Power BI, Tableau</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82347e7049db91bd</t>
+          <t>https://www.indeed.com/viewjob?jk=35918117efc7ec73</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3286,15 +3286,225 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
+          <t>AWS, Azure, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=debc73a0a4d41c46</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Senior Engineer, AI/ML Software</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Analog Devices</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=664a13900407cad4</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>HR -Data Scientist</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Renton, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b5d60890bd05332</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Data Architect 3 (Data Analyst 3)</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>University of Connecticut</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Storrs, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Oracle, SQL Server, ETL, Pentaho, Power BI, Airflow, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b2f300a70f64192</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Senior System Software Engineer - DevOps and Infrastructure Automation</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c72aec67782f8030</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Lakebase Sales Specialist-Manufacturing</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50ab1973f17e0989</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Everforth ECS</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
           <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Python</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2ec915a33af5dd7f</t>
         </is>

--- a/results/job_matches_2026-06-09.xlsx
+++ b/results/job_matches_2026-06-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,200 +678,200 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Data Engineer (Requiring GCP)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Roku</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Spark, Scala, Kafka, NoSQL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e2b721d35d7a5a7</t>
+          <t>https://www.indeed.com/viewjob?jk=a9cfe57c8aa77945</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Engineer (Requiring GCP)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SNS, ECS, IAM, RDS, Scala, PostgreSQL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=882f952f94db3f29</t>
+          <t>https://www.indeed.com/viewjob?jk=546ae471f5ede086</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer (Requiring GCP)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877524bbcd4e4f56</t>
+          <t>https://www.indeed.com/viewjob?jk=1c811d03d5aca192</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior Data Engineer (Requiring GCP)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>18.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cd0ed9ff6e64aa7</t>
+          <t>https://www.indeed.com/viewjob?jk=0b6a62dfef2d6dab</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Distinguished Software Engineer (Big Data &amp; AI)</t>
+          <t>Senior Data Engineer (Requiring GCP)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>18.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a981ef29c01bf602</t>
+          <t>https://www.indeed.com/viewjob?jk=f8656393b23155db</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>API Integrations Developer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Colorado Access</t>
+          <t>Roku</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Snowflake, SQL Server, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, GCP, Spark, Scala, Kafka, NoSQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dea7c38b1b46e2c</t>
+          <t>https://www.indeed.com/viewjob?jk=8e2b721d35d7a5a7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data/ML Engineer (AWS)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capnexus</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, API Gateway, RDS, Azure</t>
+          <t>AWS, Lambda, Kinesis, S3, SNS, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb618ea44d30c0e0</t>
+          <t>https://www.indeed.com/viewjob?jk=882f952f94db3f29</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - PGIM Technology (Hybrid - Newark, NJ)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PGIM</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7feca5e666659d5</t>
+          <t>https://www.indeed.com/viewjob?jk=877524bbcd4e4f56</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - PGIM Technology</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ddb3e15556877d</t>
+          <t>https://www.indeed.com/viewjob?jk=7cd0ed9ff6e64aa7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Analytics</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lovevery</t>
+          <t>Capstone Logistics, LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Peachtree Corners, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b019f71f6d426d97</t>
+          <t>https://www.indeed.com/viewjob?jk=30d85c0bd52ccea6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior DevOps/Platform Engineer</t>
+          <t>Distinguished Software Engineer (Big Data &amp; AI)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JITSU</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc401e882f1b7d3b</t>
+          <t>https://www.indeed.com/viewjob?jk=a981ef29c01bf602</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer</t>
+          <t>API Integrations Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>Colorado Access</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Dataflow, Scala, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Snowflake, SQL Server, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d4021156adfe1b</t>
+          <t>https://www.indeed.com/viewjob?jk=3dea7c38b1b46e2c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering</t>
+          <t>Senior Data/ML Engineer (AWS)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Capnexus</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, API Gateway, RDS, Azure</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06eee63ec8fb01b9</t>
+          <t>https://www.indeed.com/viewjob?jk=bb618ea44d30c0e0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Engineer, Investment Technology</t>
+          <t>Senior Data Engineer - PGIM Technology (Hybrid - Newark, NJ)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>PGIM</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, IAM, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,102 +1161,102 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e247743b45089523</t>
+          <t>https://www.indeed.com/viewjob?jk=b7feca5e666659d5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Full Stack Engineer</t>
+          <t>Senior Data Engineer - PGIM Technology</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>L&amp;T Technology Services Ltd.</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Cloud Storage, Spark, Scala, MySQL, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c4b06a84a76fe1</t>
+          <t>https://www.indeed.com/viewjob?jk=42ddb3e15556877d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer, Analytics</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DTN</t>
+          <t>Lovevery</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb35c7b57058adb4</t>
+          <t>https://www.indeed.com/viewjob?jk=b019f71f6d426d97</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Specialist Solutions Architect - Data Engineering</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10ead8343cec4879</t>
+          <t>https://www.indeed.com/viewjob?jk=06eee63ec8fb01b9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer, Investment Technology</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, Lambda, Athena, S3, IAM, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=162c2ab9f292809c</t>
+          <t>https://www.indeed.com/viewjob?jk=e247743b45089523</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Full Stack Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>L&amp;T Technology Services Ltd.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, S3, IAM, Cloud Storage, Spark, Scala, MySQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7be54a20fbf4431</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c4b06a84a76fe1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>DTN</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, BigQuery, Cloud Storage, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6773c1c434a7ae57</t>
+          <t>https://www.indeed.com/viewjob?jk=cb35c7b57058adb4</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5232892f9a4a9b08</t>
+          <t>https://www.indeed.com/viewjob?jk=10ead8343cec4879</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior AI Operations Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd1103c64558f430</t>
+          <t>https://www.indeed.com/viewjob?jk=162c2ab9f292809c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d135475bf2adc12</t>
+          <t>https://www.indeed.com/viewjob?jk=d7be54a20fbf4431</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>HealthStream</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, BigQuery, Cloud Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6929e10d2183d6c</t>
+          <t>https://www.indeed.com/viewjob?jk=6773c1c434a7ae57</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior BI Data Engineer</t>
+          <t>Senior Data Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Soleo Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dedc6497a9161a47</t>
+          <t>https://www.indeed.com/viewjob?jk=5232892f9a4a9b08</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Operations Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DTN</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33d845a6e90fbede</t>
+          <t>https://www.indeed.com/viewjob?jk=dd1103c64558f430</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Development Engineer (Core Engine)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e32c70852b2e7e9</t>
+          <t>https://www.indeed.com/viewjob?jk=8d135475bf2adc12</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Development Engineer (Core Engine)</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Carollo Engineers, Inc.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>Azure, Synapse Analytics, Spark, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f53654a42d5f44e</t>
+          <t>https://www.indeed.com/viewjob?jk=ab80492ce8c08674</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Development Engineer (Core Engine)</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>HealthStream</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74408bc2ca90f29e</t>
+          <t>https://www.indeed.com/viewjob?jk=c6929e10d2183d6c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Development Engineer (Core Engine)</t>
+          <t>Sr. Engineer, Site Reliability</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Syniti</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, S3, SQS, IAM, RDS, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,19 +1721,19 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfcd3234ed7c76b1</t>
+          <t>https://www.indeed.com/viewjob?jk=0a9aaaa695359595</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer</t>
+          <t>Senior BI Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Digital Consultants</t>
+          <t>Soleo Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1742,11 +1742,11 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, SQS, ECS, Azure, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5b05b32ba6e729a</t>
+          <t>https://www.indeed.com/viewjob?jk=dedc6497a9161a47</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NIKSUN, Inc.</t>
+          <t>DTN</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fd5208875d3c1b2</t>
+          <t>https://www.indeed.com/viewjob?jk=33d845a6e90fbede</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer</t>
+          <t>Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SWBC</t>
+          <t>Digital Consultants</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, SQS, ECS, Azure, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=075826e3e1704244</t>
+          <t>https://www.indeed.com/viewjob?jk=d5b05b32ba6e729a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Engineer 2: AI Agentic Platform (Hybrid - Seattle, WA)</t>
+          <t>Senior Development Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1a42d221dac8991</t>
+          <t>https://www.indeed.com/viewjob?jk=4e32c70852b2e7e9</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CD&amp;A Data Engineer</t>
+          <t>Senior Development Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6cb0aa04ee83dc1</t>
+          <t>https://www.indeed.com/viewjob?jk=3f53654a42d5f44e</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer – Python + React (Healthcare Domain)</t>
+          <t>Senior Development Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nova Web Technologies</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff5c44492f4137d0</t>
+          <t>https://www.indeed.com/viewjob?jk=74408bc2ca90f29e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DBX/PowerBI Developer</t>
+          <t>Senior Development Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Cloud Storage, Spark, Scala, Snowflake, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1532e72abbad0fcf</t>
+          <t>https://www.indeed.com/viewjob?jk=cfcd3234ed7c76b1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NIKSUN, Inc.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Spark, Snowflake, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline, Terraform</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f417fbf524598c0</t>
+          <t>https://www.indeed.com/viewjob?jk=0fd5208875d3c1b2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Azure Engineer (Associate)</t>
+          <t>CD&amp;A Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>RDS, Azure, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dbe236b626e4a53</t>
+          <t>https://www.indeed.com/viewjob?jk=54bc52360158a211</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer (Advanced Threat Protection)</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>SWBC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Terraform, Git</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2c3719c3e2ec42</t>
+          <t>https://www.indeed.com/viewjob?jk=075826e3e1704244</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Engineer 2: AI Agentic Platform (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be9e819ada5cf6a</t>
+          <t>https://www.indeed.com/viewjob?jk=e1a42d221dac8991</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior SQL Developer</t>
+          <t>CD&amp;A Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
+          <t>RDS, Azure, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b418f223555b73b9</t>
+          <t>https://www.indeed.com/viewjob?jk=f6cb0aa04ee83dc1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Data Engineer – Python + React (Healthcare Domain)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>Nova Web Technologies</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707d30063b198a61</t>
+          <t>https://www.indeed.com/viewjob?jk=ff5c44492f4137d0</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SQL Platform Engineer</t>
+          <t>Production Digitalization Intern (Fall 2026)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>BMW Group</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Woodruff, SC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Athena, RDS, Azure, Oracle, PostgreSQL, ETL, ELT, Amazon QuickSight</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e965a90207e77c</t>
+          <t>https://www.indeed.com/viewjob?jk=6d2c3fbbbf2753ab</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>DBX/PowerBI Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CNA Insurance</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Cloud Storage, Spark, Scala, Snowflake, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947710ea68d4354a</t>
+          <t>https://www.indeed.com/viewjob?jk=1532e72abbad0fcf</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Rise Collective</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, NoSQL</t>
+          <t>AWS, Glue, RDS, Spark, Snowflake, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff3b252b91a197e5</t>
+          <t>https://www.indeed.com/viewjob?jk=1f417fbf524598c0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Engineer (Associate)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Crumbl Cookies Franchises</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60db0ac4d21d1076</t>
+          <t>https://www.indeed.com/viewjob?jk=9dbe236b626e4a53</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Cloud Infrastructure Engineer (Advanced Threat Protection)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Crumbl Cookies Franchises</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, GCP, BigQuery, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,14 +2351,14 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c53bb7a7aa686c9</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2c3719c3e2ec42</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55da546db249541e</t>
+          <t>https://www.indeed.com/viewjob?jk=3be9e819ada5cf6a</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer, IT Software</t>
+          <t>Senior SQL Developer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cde05fe8d78b7bea</t>
+          <t>https://www.indeed.com/viewjob?jk=b418f223555b73b9</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (.NET )</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,19 +2456,19 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8fae101fea70214</t>
+          <t>https://www.indeed.com/viewjob?jk=707d30063b198a61</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Blockchain Engineer</t>
+          <t>SQL Platform Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=678a055b3ce18049</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e965a90207e77c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineering Senior Advisor- Hybrid</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>CNA Insurance</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Spark Streaming, Kafka, Oracle, MongoDB, NoSQL, Splunk, CI/CD</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ab95bf144a98568</t>
+          <t>https://www.indeed.com/viewjob?jk=947710ea68d4354a</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineering Senior Advisor- Hybrid</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Spark Streaming, Kafka, Oracle, MongoDB, NoSQL, Splunk, CI/CD</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceca754c6b6fbfd5</t>
+          <t>https://www.indeed.com/viewjob?jk=257bf20abcf10b52</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Rise Collective</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5abed50f2367d51</t>
+          <t>https://www.indeed.com/viewjob?jk=ff3b252b91a197e5</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Crumbl Cookies Franchises</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,42 +2621,42 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92370ed8cefd2963</t>
+          <t>https://www.indeed.com/viewjob?jk=60db0ac4d21d1076</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Crumbl Cookies Franchises</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b9a027a38e2401</t>
+          <t>https://www.indeed.com/viewjob?jk=4c53bb7a7aa686c9</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineering Senior Advisor- Hybrid</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Spurs Sports &amp; Entertainment</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Spark, Spark Streaming, Kafka, Oracle, MongoDB, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31a3c71dc92d0e0c</t>
+          <t>https://www.indeed.com/viewjob?jk=1ab95bf144a98568</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer, Go to Market (Remote)</t>
+          <t>Software Engineering Senior Advisor- Hybrid</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, RDS, Spark, Spark Streaming, Kafka, Oracle, MongoDB, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27f893425f230116</t>
+          <t>https://www.indeed.com/viewjob?jk=ceca754c6b6fbfd5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Software Engineer (.NET )</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Metronet</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8988ab1d912fc2fc</t>
+          <t>https://www.indeed.com/viewjob?jk=a8fae101fea70214</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Offchain Labs</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, CodeBuild, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a00c080490fe5a6</t>
+          <t>https://www.indeed.com/viewjob?jk=55da546db249541e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
+          <t>Sr Associate Engineer, IT Software</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,28 +2841,28 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2de73d2117d18151</t>
+          <t>https://www.indeed.com/viewjob?jk=cde05fe8d78b7bea</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Frontend Software Engineer</t>
+          <t>Senior Blockchain Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Dresser Utility Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e77c6f0d763f738</t>
+          <t>https://www.indeed.com/viewjob?jk=678a055b3ce18049</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer II, Wayfair Sponsored Shops</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1700b3ad8a2acabe</t>
+          <t>https://www.indeed.com/viewjob?jk=18b9a027a38e2401</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>Sr. Power BI Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>IQVIA</t>
+          <t>Hussmann</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Bridgeton, MO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Hive, Spark, PySpark, Scala, ETL, ELT, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=409022a27d0ec067</t>
+          <t>https://www.indeed.com/viewjob?jk=454d2924e4649642</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer - Senior Associate</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>Spurs Sports &amp; Entertainment</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Hadoop, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b998a3d5965b93e8</t>
+          <t>https://www.indeed.com/viewjob?jk=31a3c71dc92d0e0c</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer, Go to Market (Remote)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Redford, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29332168c78c58c</t>
+          <t>https://www.indeed.com/viewjob?jk=27f893425f230116</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Metronet</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d23e98febb4af71d</t>
+          <t>https://www.indeed.com/viewjob?jk=8988ab1d912fc2fc</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Snooze an AM Eatery</t>
+          <t>Offchain Labs</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, CodeBuild, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65eaed35b3d68901</t>
+          <t>https://www.indeed.com/viewjob?jk=8a00c080490fe5a6</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Junior Data Engineer (Faculty Specialist)</t>
+          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>University of Maryland University College</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>College Park, MD, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Hive, Spark, SQL Server, PostgreSQL, Cassandra, ETL, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaedc5d1808c1ed5</t>
+          <t>https://www.indeed.com/viewjob?jk=2de73d2117d18151</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platforms &amp; Monetization</t>
+          <t>Frontend Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Wowza Media Systems</t>
+          <t>Dresser Utility Solutions</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, MySQL, Data Modeling, ETL, REST API integration, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa5b3c703b2170b9</t>
+          <t>https://www.indeed.com/viewjob?jk=2e77c6f0d763f738</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Software Engineer II, Wayfair Sponsored Shops</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=953100d783ca43ac</t>
+          <t>https://www.indeed.com/viewjob?jk=1700b3ad8a2acabe</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, Glue, EMR, Hive, Spark, PySpark, Scala, ETL, ELT, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72b083a5bbeb1232</t>
+          <t>https://www.indeed.com/viewjob?jk=409022a27d0ec067</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Data Engineer - Senior Associate</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Hadoop, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35918117efc7ec73</t>
+          <t>https://www.indeed.com/viewjob?jk=b998a3d5965b93e8</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Redford, MI, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=debc73a0a4d41c46</t>
+          <t>https://www.indeed.com/viewjob?jk=c29332168c78c58c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Engineer, AI/ML Software</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Analog Devices</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=664a13900407cad4</t>
+          <t>https://www.indeed.com/viewjob?jk=d23e98febb4af71d</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>HR -Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Snooze an AM Eatery</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, Airflow</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b5d60890bd05332</t>
+          <t>https://www.indeed.com/viewjob?jk=65eaed35b3d68901</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Architect 3 (Data Analyst 3)</t>
+          <t>Junior Data Engineer (Faculty Specialist)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>University of Connecticut</t>
+          <t>University of Maryland University College</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Storrs, CT, US USA</t>
+          <t>College Park, MD, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, ETL, Pentaho, Power BI, Airflow, Python, SQL</t>
+          <t>AWS, GCP, Hadoop, Hive, Spark, SQL Server, PostgreSQL, Cassandra, ETL, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b2f300a70f64192</t>
+          <t>https://www.indeed.com/viewjob?jk=aaedc5d1808c1ed5</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior System Software Engineer - DevOps and Infrastructure Automation</t>
+          <t>Senior Software Engineer, Data Platforms &amp; Monetization</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Wowza Media Systems</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, S3, RDS, MySQL, Data Modeling, ETL, REST API integration, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c72aec67782f8030</t>
+          <t>https://www.indeed.com/viewjob?jk=aa5b3c703b2170b9</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Lakebase Sales Specialist-Manufacturing</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50ab1973f17e0989</t>
+          <t>https://www.indeed.com/viewjob?jk=953100d783ca43ac</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,17 +3496,262 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, Docker</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=72b083a5bbeb1232</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>The Carlyle Group</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=35918117efc7ec73</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=debc73a0a4d41c46</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Senior Engineer, AI/ML Software</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Analog Devices</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=664a13900407cad4</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Data Architect 3 (Data Analyst 3)</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>University of Connecticut</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Storrs, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Oracle, SQL Server, ETL, Pentaho, Power BI, Airflow, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b2f300a70f64192</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Lakebase Sales Specialist-Manufacturing</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50ab1973f17e0989</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Everforth ECS</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
           <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Python</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2ec915a33af5dd7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>HR -Data Scientist</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Renton, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b5d60890bd05332</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-09.xlsx
+++ b/results/job_matches_2026-06-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>API Integrations Developer</t>
+          <t>AI Solution Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Colorado Access</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Snowflake, SQL Server, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, ECS, RDS, Vertex AI, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dea7c38b1b46e2c</t>
+          <t>https://www.indeed.com/viewjob?jk=f647259c84954990</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data/ML Engineer (AWS)</t>
+          <t>API Integrations Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capnexus</t>
+          <t>Colorado Access</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, API Gateway, RDS, Azure</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Snowflake, SQL Server, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb618ea44d30c0e0</t>
+          <t>https://www.indeed.com/viewjob?jk=3dea7c38b1b46e2c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - PGIM Technology (Hybrid - Newark, NJ)</t>
+          <t>Senior Data/ML Engineer (AWS)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PGIM</t>
+          <t>Capnexus</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, API Gateway, RDS, Azure</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,19 +1161,19 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7feca5e666659d5</t>
+          <t>https://www.indeed.com/viewjob?jk=bb618ea44d30c0e0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - PGIM Technology</t>
+          <t>Senior Data Engineer - PGIM Technology (Hybrid - Newark, NJ)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>PGIM</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ddb3e15556877d</t>
+          <t>https://www.indeed.com/viewjob?jk=b7feca5e666659d5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Analytics</t>
+          <t>Senior Data Engineer - PGIM Technology</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lovevery</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b019f71f6d426d97</t>
+          <t>https://www.indeed.com/viewjob?jk=42ddb3e15556877d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering</t>
+          <t>Senior Data Engineer, Analytics</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Lovevery</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06eee63ec8fb01b9</t>
+          <t>https://www.indeed.com/viewjob?jk=b019f71f6d426d97</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Engineer, Investment Technology</t>
+          <t>Specialist Solutions Architect - Data Engineering</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, IAM, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,59 +1301,59 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e247743b45089523</t>
+          <t>https://www.indeed.com/viewjob?jk=06eee63ec8fb01b9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Full Stack Engineer</t>
+          <t>Senior Engineer, Investment Technology</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>L&amp;T Technology Services Ltd.</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Cloud Storage, Spark, Scala, MySQL, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, Athena, S3, IAM, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c4b06a84a76fe1</t>
+          <t>https://www.indeed.com/viewjob?jk=e247743b45089523</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Full Stack Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DTN</t>
+          <t>L&amp;T Technology Services Ltd.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, S3, IAM, Cloud Storage, Spark, Scala, MySQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb35c7b57058adb4</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c4b06a84a76fe1</t>
         </is>
       </c>
     </row>
@@ -1383,12 +1383,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>DTN</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10ead8343cec4879</t>
+          <t>https://www.indeed.com/viewjob?jk=cb35c7b57058adb4</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=162c2ab9f292809c</t>
+          <t>https://www.indeed.com/viewjob?jk=10ead8343cec4879</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7be54a20fbf4431</t>
+          <t>https://www.indeed.com/viewjob?jk=162c2ab9f292809c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, BigQuery, Cloud Storage, Scala, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6773c1c434a7ae57</t>
+          <t>https://www.indeed.com/viewjob?jk=d7be54a20fbf4431</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Software Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, BigQuery, Cloud Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5232892f9a4a9b08</t>
+          <t>https://www.indeed.com/viewjob?jk=6773c1c434a7ae57</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior AI Operations Engineer</t>
+          <t>Senior Data Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd1103c64558f430</t>
+          <t>https://www.indeed.com/viewjob?jk=5232892f9a4a9b08</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Operations Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d135475bf2adc12</t>
+          <t>https://www.indeed.com/viewjob?jk=dd1103c64558f430</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Carollo Engineers, Inc.</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Spark, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab80492ce8c08674</t>
+          <t>https://www.indeed.com/viewjob?jk=8d135475bf2adc12</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HealthStream</t>
+          <t>Carollo Engineers, Inc.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, DynamoDB, CI/CD</t>
+          <t>Azure, Synapse Analytics, Spark, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6929e10d2183d6c</t>
+          <t>https://www.indeed.com/viewjob?jk=ab80492ce8c08674</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Site Reliability</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Syniti</t>
+          <t>HealthStream</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, IAM, RDS, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a9aaaa695359595</t>
+          <t>https://www.indeed.com/viewjob?jk=c6929e10d2183d6c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior BI Data Engineer</t>
+          <t>Sr. Engineer, Site Reliability</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Soleo Health</t>
+          <t>Syniti</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, SQS, IAM, RDS, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dedc6497a9161a47</t>
+          <t>https://www.indeed.com/viewjob?jk=0a9aaaa695359595</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior BI Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DTN</t>
+          <t>Soleo Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, ELT, CI/CD</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33d845a6e90fbede</t>
+          <t>https://www.indeed.com/viewjob?jk=dedc6497a9161a47</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Digital Consultants</t>
+          <t>DTN</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, SQS, ECS, Azure, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5b05b32ba6e729a</t>
+          <t>https://www.indeed.com/viewjob?jk=33d845a6e90fbede</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Development Engineer (Core Engine)</t>
+          <t>Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Digital Consultants</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, SQS, ECS, Azure, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e32c70852b2e7e9</t>
+          <t>https://www.indeed.com/viewjob?jk=d5b05b32ba6e729a</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f53654a42d5f44e</t>
+          <t>https://www.indeed.com/viewjob?jk=4e32c70852b2e7e9</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74408bc2ca90f29e</t>
+          <t>https://www.indeed.com/viewjob?jk=3f53654a42d5f44e</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfcd3234ed7c76b1</t>
+          <t>https://www.indeed.com/viewjob?jk=74408bc2ca90f29e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Development Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NIKSUN, Inc.</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,59 +2001,59 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fd5208875d3c1b2</t>
+          <t>https://www.indeed.com/viewjob?jk=cfcd3234ed7c76b1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CD&amp;A Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>NIKSUN, Inc.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54bc52360158a211</t>
+          <t>https://www.indeed.com/viewjob?jk=0fd5208875d3c1b2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer</t>
+          <t>CD&amp;A Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SWBC</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=075826e3e1704244</t>
+          <t>https://www.indeed.com/viewjob?jk=54bc52360158a211</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Engineer 2: AI Agentic Platform (Hybrid - Seattle, WA)</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>SWBC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1a42d221dac8991</t>
+          <t>https://www.indeed.com/viewjob?jk=075826e3e1704244</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CD&amp;A Data Engineer</t>
+          <t>Senior Engineer 2: AI Agentic Platform (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6cb0aa04ee83dc1</t>
+          <t>https://www.indeed.com/viewjob?jk=e1a42d221dac8991</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer – Python + React (Healthcare Domain)</t>
+          <t>CD&amp;A Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Nova Web Technologies</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff5c44492f4137d0</t>
+          <t>https://www.indeed.com/viewjob?jk=f6cb0aa04ee83dc1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Production Digitalization Intern (Fall 2026)</t>
+          <t>Data Engineer – Python + React (Healthcare Domain)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BMW Group</t>
+          <t>Nova Web Technologies</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Woodruff, SC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, RDS, Azure, Oracle, PostgreSQL, ETL, ELT, Amazon QuickSight</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d2c3fbbbf2753ab</t>
+          <t>https://www.indeed.com/viewjob?jk=ff5c44492f4137d0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DBX/PowerBI Developer</t>
+          <t>Production Digitalization Intern (Fall 2026)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>BMW Group</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Woodruff, SC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Cloud Storage, Spark, Scala, Snowflake, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, Athena, RDS, Azure, Oracle, PostgreSQL, ETL, ELT, Amazon QuickSight</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1532e72abbad0fcf</t>
+          <t>https://www.indeed.com/viewjob?jk=6d2c3fbbbf2753ab</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>DBX/PowerBI Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Spark, Snowflake, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline, Terraform</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Cloud Storage, Spark, Scala, Snowflake, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f417fbf524598c0</t>
+          <t>https://www.indeed.com/viewjob?jk=1532e72abbad0fcf</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Azure Engineer (Associate)</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Glue, RDS, Spark, Snowflake, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dbe236b626e4a53</t>
+          <t>https://www.indeed.com/viewjob?jk=1f417fbf524598c0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer (Advanced Threat Protection)</t>
+          <t>Azure Engineer (Associate)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Terraform, Git</t>
+          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2c3719c3e2ec42</t>
+          <t>https://www.indeed.com/viewjob?jk=9dbe236b626e4a53</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Sr Cloud Infrastructure Engineer (Advanced Threat Protection)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, GCP, BigQuery, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be9e819ada5cf6a</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2c3719c3e2ec42</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior SQL Developer</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>CNA Insurance</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b418f223555b73b9</t>
+          <t>https://www.indeed.com/viewjob?jk=947710ea68d4354a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Senior Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>Rise Collective</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707d30063b198a61</t>
+          <t>https://www.indeed.com/viewjob?jk=ff3b252b91a197e5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SQL Platform Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e965a90207e77c</t>
+          <t>https://www.indeed.com/viewjob?jk=3be9e819ada5cf6a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Senior SQL Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CNA Insurance</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947710ea68d4354a</t>
+          <t>https://www.indeed.com/viewjob?jk=b418f223555b73b9</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=257bf20abcf10b52</t>
+          <t>https://www.indeed.com/viewjob?jk=707d30063b198a61</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>SQL Platform Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Rise Collective</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff3b252b91a197e5</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e965a90207e77c</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Crumbl Cookies Franchises</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60db0ac4d21d1076</t>
+          <t>https://www.indeed.com/viewjob?jk=257bf20abcf10b52</t>
         </is>
       </c>
     </row>
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c53bb7a7aa686c9</t>
+          <t>https://www.indeed.com/viewjob?jk=60db0ac4d21d1076</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineering Senior Advisor- Hybrid</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Crumbl Cookies Franchises</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Spark Streaming, Kafka, Oracle, MongoDB, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ab95bf144a98568</t>
+          <t>https://www.indeed.com/viewjob?jk=4c53bb7a7aa686c9</t>
         </is>
       </c>
     </row>
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceca754c6b6fbfd5</t>
+          <t>https://www.indeed.com/viewjob?jk=1ab95bf144a98568</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (.NET )</t>
+          <t>Software Engineering Senior Advisor- Hybrid</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Spark, Spark Streaming, Kafka, Oracle, MongoDB, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8fae101fea70214</t>
+          <t>https://www.indeed.com/viewjob?jk=ceca754c6b6fbfd5</t>
         </is>
       </c>
     </row>
@@ -2848,17 +2848,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Blockchain Engineer</t>
+          <t>Senior Software Engineer (.NET )</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=678a055b3ce18049</t>
+          <t>https://www.indeed.com/viewjob?jk=a8fae101fea70214</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Blockchain Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b9a027a38e2401</t>
+          <t>https://www.indeed.com/viewjob?jk=678a055b3ce18049</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Power BI Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Hussmann</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bridgeton, MO, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=454d2924e4649642</t>
+          <t>https://www.indeed.com/viewjob?jk=18b9a027a38e2401</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Power BI Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Spurs Sports &amp; Entertainment</t>
+          <t>Hussmann</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Bridgeton, MO, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31a3c71dc92d0e0c</t>
+          <t>https://www.indeed.com/viewjob?jk=454d2924e4649642</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer, Go to Market (Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Spurs Sports &amp; Entertainment</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27f893425f230116</t>
+          <t>https://www.indeed.com/viewjob?jk=31a3c71dc92d0e0c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer, Go to Market (Remote)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Metronet</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8988ab1d912fc2fc</t>
+          <t>https://www.indeed.com/viewjob?jk=27f893425f230116</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Offchain Labs</t>
+          <t>Metronet</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, CodeBuild, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a00c080490fe5a6</t>
+          <t>https://www.indeed.com/viewjob?jk=8988ab1d912fc2fc</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>Offchain Labs</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, CodeBuild, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2de73d2117d18151</t>
+          <t>https://www.indeed.com/viewjob?jk=8a00c080490fe5a6</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Frontend Software Engineer</t>
+          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Dresser Utility Solutions</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e77c6f0d763f738</t>
+          <t>https://www.indeed.com/viewjob?jk=2de73d2117d18151</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer II, Wayfair Sponsored Shops</t>
+          <t>Frontend Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>Dresser Utility Solutions</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1700b3ad8a2acabe</t>
+          <t>https://www.indeed.com/viewjob?jk=2e77c6f0d763f738</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>Software Engineer II, Wayfair Sponsored Shops</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>IQVIA</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Hive, Spark, PySpark, Scala, ETL, ELT, Terraform</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=409022a27d0ec067</t>
+          <t>https://www.indeed.com/viewjob?jk=1700b3ad8a2acabe</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer - Senior Associate</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Hadoop, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, EMR, Hive, Spark, PySpark, Scala, ETL, ELT, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b998a3d5965b93e8</t>
+          <t>https://www.indeed.com/viewjob?jk=409022a27d0ec067</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Senior Associate</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Redford, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Hadoop, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29332168c78c58c</t>
+          <t>https://www.indeed.com/viewjob?jk=b998a3d5965b93e8</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Redford, MI, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d23e98febb4af71d</t>
+          <t>https://www.indeed.com/viewjob?jk=c29332168c78c58c</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Snooze an AM Eatery</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, Airflow</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65eaed35b3d68901</t>
+          <t>https://www.indeed.com/viewjob?jk=d23e98febb4af71d</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Junior Data Engineer (Faculty Specialist)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>University of Maryland University College</t>
+          <t>Snooze an AM Eatery</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>College Park, MD, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Hive, Spark, SQL Server, PostgreSQL, Cassandra, ETL, Git</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, Airflow</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaedc5d1808c1ed5</t>
+          <t>https://www.indeed.com/viewjob?jk=65eaed35b3d68901</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platforms &amp; Monetization</t>
+          <t>Junior Data Engineer (Faculty Specialist)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Wowza Media Systems</t>
+          <t>University of Maryland University College</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>College Park, MD, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, MySQL, Data Modeling, ETL, REST API integration, Terraform</t>
+          <t>AWS, GCP, Hadoop, Hive, Spark, SQL Server, PostgreSQL, Cassandra, ETL, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,19 +3436,19 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa5b3c703b2170b9</t>
+          <t>https://www.indeed.com/viewjob?jk=aaedc5d1808c1ed5</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Software Engineer, Data Platforms &amp; Monetization</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Wowza Media Systems</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, Glue, Lambda, S3, RDS, MySQL, Data Modeling, ETL, REST API integration, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=953100d783ca43ac</t>
+          <t>https://www.indeed.com/viewjob?jk=aa5b3c703b2170b9</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>The Carlyle Group</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72b083a5bbeb1232</t>
+          <t>https://www.indeed.com/viewjob?jk=35918117efc7ec73</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
+          <t>AWS, Azure, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35918117efc7ec73</t>
+          <t>https://www.indeed.com/viewjob?jk=debc73a0a4d41c46</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Engineer, AI/ML Software</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Analog Devices</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=debc73a0a4d41c46</t>
+          <t>https://www.indeed.com/viewjob?jk=664a13900407cad4</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Engineer, AI/ML Software</t>
+          <t>Lakebase Sales Specialist-Manufacturing</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Analog Devices</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=664a13900407cad4</t>
+          <t>https://www.indeed.com/viewjob?jk=50ab1973f17e0989</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Architect 3 (Data Analyst 3)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>University of Connecticut</t>
+          <t>Everforth ECS</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Storrs, CT, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, ETL, Pentaho, Power BI, Airflow, Python, SQL</t>
+          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Python</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b2f300a70f64192</t>
+          <t>https://www.indeed.com/viewjob?jk=2ec915a33af5dd7f</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Lakebase Sales Specialist-Manufacturing</t>
+          <t>HR -Data Scientist</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50ab1973f17e0989</t>
+          <t>https://www.indeed.com/viewjob?jk=2b5d60890bd05332</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Architect 3 (Data Analyst 3)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>University of Connecticut</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Storrs, CT, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Python</t>
+          <t>RDS, Scala, Oracle, SQL Server, ETL, Pentaho, Power BI, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,42 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ec915a33af5dd7f</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>HR -Data Scientist</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Renton, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2b5d60890bd05332</t>
+          <t>https://www.indeed.com/viewjob?jk=3b2f300a70f64192</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-09.xlsx
+++ b/results/job_matches_2026-06-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineering Senior Advisor- Hybrid</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>The Motley Fool</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.5</v>
+        <v>20.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, API Gateway, IAM, RDS, Databricks, Spark</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, Snowflake, clustering keys, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d42d7af82b11801</t>
+          <t>https://www.indeed.com/viewjob?jk=76c7190df188f528</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer Senior</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Motley Fool</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, Snowflake, clustering keys, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Sqoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76c7190df188f528</t>
+          <t>https://www.indeed.com/viewjob?jk=d18ea85c2c928c35</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer Senior</t>
+          <t>Software Engineer III - Data Platform</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Sqoop, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Databricks, Unity Catalog, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d18ea85c2c928c35</t>
+          <t>https://www.indeed.com/viewjob?jk=257ec7c1915b24c6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Platform</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Databricks, Unity Catalog, Spark</t>
+          <t>AWS, API Gateway, IAM, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,42 +636,42 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=257ec7c1915b24c6</t>
+          <t>https://www.indeed.com/viewjob?jk=2da5893cfc35a86b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AI Engineer - AI/ML</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Vertex AI, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2da5893cfc35a86b</t>
+          <t>https://www.indeed.com/viewjob?jk=603c741187a35795</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Data Bricks Migration and Support engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
+          <t>AWS, IAM, Azure, Data Factory, Databricks, Blob Storage, Unity Catalog, Delta Live Tables, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cd0ed9ff6e64aa7</t>
+          <t>https://www.indeed.com/viewjob?jk=f89526bd8706b6bf</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capstone Logistics, LLC</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Peachtree Corners, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,104 +1011,104 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30d85c0bd52ccea6</t>
+          <t>https://www.indeed.com/viewjob?jk=7cd0ed9ff6e64aa7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Distinguished Software Engineer (Big Data &amp; AI)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a981ef29c01bf602</t>
+          <t>https://www.indeed.com/viewjob?jk=9652a3e159336480</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Solution Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Capstone Logistics, LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Peachtree Corners, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, ECS, RDS, Vertex AI, Spark, Scala, MLOps, MLflow</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f647259c84954990</t>
+          <t>https://www.indeed.com/viewjob?jk=30d85c0bd52ccea6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>API Integrations Developer</t>
+          <t>Distinguished Software Engineer (Big Data &amp; AI)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Colorado Access</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Snowflake, SQL Server, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dea7c38b1b46e2c</t>
+          <t>https://www.indeed.com/viewjob?jk=a981ef29c01bf602</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data/ML Engineer (AWS)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capnexus</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, API Gateway, RDS, Azure</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb618ea44d30c0e0</t>
+          <t>https://www.indeed.com/viewjob?jk=4e1214688100a67a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - PGIM Technology (Hybrid - Newark, NJ)</t>
+          <t>API Integrations Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PGIM</t>
+          <t>Colorado Access</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Snowflake, SQL Server, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7feca5e666659d5</t>
+          <t>https://www.indeed.com/viewjob?jk=3dea7c38b1b46e2c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - PGIM Technology</t>
+          <t>Senior Data/ML Engineer (AWS)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>Capnexus</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, API Gateway, RDS, Azure</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ddb3e15556877d</t>
+          <t>https://www.indeed.com/viewjob?jk=bb618ea44d30c0e0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Analytics</t>
+          <t>Senior Data Engineer - PGIM Technology (Hybrid - Newark, NJ)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Lovevery</t>
+          <t>PGIM</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b019f71f6d426d97</t>
+          <t>https://www.indeed.com/viewjob?jk=b7feca5e666659d5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering</t>
+          <t>Senior Data Engineer - PGIM Technology</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06eee63ec8fb01b9</t>
+          <t>https://www.indeed.com/viewjob?jk=42ddb3e15556877d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Engineer, Investment Technology</t>
+          <t>Senior Data Engineer, Analytics</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Lovevery</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,77 +1326,77 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, IAM, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e247743b45089523</t>
+          <t>https://www.indeed.com/viewjob?jk=b019f71f6d426d97</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI Full Stack Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>L&amp;T Technology Services Ltd.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Cloud Storage, Spark, Scala, MySQL, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c4b06a84a76fe1</t>
+          <t>https://www.indeed.com/viewjob?jk=34801161eca101a2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data/Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DTN</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Spark, Scala, Data Modeling, ETL, dbt, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb35c7b57058adb4</t>
+          <t>https://www.indeed.com/viewjob?jk=260e9231f9bc608e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Specialist Solutions Architect - Data Engineering</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10ead8343cec4879</t>
+          <t>https://www.indeed.com/viewjob?jk=06eee63ec8fb01b9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Full Stack Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>L&amp;T Technology Services Ltd.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, S3, IAM, Cloud Storage, Spark, Scala, MySQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=162c2ab9f292809c</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c4b06a84a76fe1</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>DTN</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7be54a20fbf4431</t>
+          <t>https://www.indeed.com/viewjob?jk=cb35c7b57058adb4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, BigQuery, Cloud Storage, Scala, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6773c1c434a7ae57</t>
+          <t>https://www.indeed.com/viewjob?jk=10ead8343cec4879</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5232892f9a4a9b08</t>
+          <t>https://www.indeed.com/viewjob?jk=162c2ab9f292809c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior AI Operations Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd1103c64558f430</t>
+          <t>https://www.indeed.com/viewjob?jk=d7be54a20fbf4431</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, BigQuery, Cloud Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d135475bf2adc12</t>
+          <t>https://www.indeed.com/viewjob?jk=6773c1c434a7ae57</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior Data Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Carollo Engineers, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Spark, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab80492ce8c08674</t>
+          <t>https://www.indeed.com/viewjob?jk=5232892f9a4a9b08</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Senior AI Operations Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HealthStream</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6929e10d2183d6c</t>
+          <t>https://www.indeed.com/viewjob?jk=dd1103c64558f430</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Site Reliability</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Syniti</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, IAM, RDS, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a9aaaa695359595</t>
+          <t>https://www.indeed.com/viewjob?jk=8d135475bf2adc12</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior BI Data Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Soleo Health</t>
+          <t>Carollo Engineers, Inc.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>Azure, Synapse Analytics, Spark, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dedc6497a9161a47</t>
+          <t>https://www.indeed.com/viewjob?jk=ab80492ce8c08674</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DTN</t>
+          <t>HealthStream</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33d845a6e90fbede</t>
+          <t>https://www.indeed.com/viewjob?jk=c6929e10d2183d6c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer</t>
+          <t>Sr. Engineer, Site Reliability</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Digital Consultants</t>
+          <t>Syniti</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, SQS, ECS, Azure, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, SQS, IAM, RDS, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5b05b32ba6e729a</t>
+          <t>https://www.indeed.com/viewjob?jk=0a9aaaa695359595</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Development Engineer (Core Engine)</t>
+          <t>Senior BI Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Soleo Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e32c70852b2e7e9</t>
+          <t>https://www.indeed.com/viewjob?jk=dedc6497a9161a47</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Development Engineer (Core Engine)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>DTN</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f53654a42d5f44e</t>
+          <t>https://www.indeed.com/viewjob?jk=33d845a6e90fbede</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Development Engineer (Core Engine)</t>
+          <t>Powertrain Embedded ASW , DevOps and Compiler Toolchain Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, ETL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74408bc2ca90f29e</t>
+          <t>https://www.indeed.com/viewjob?jk=022045c10afd20b1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Development Engineer (Core Engine)</t>
+          <t>Full-Stack Software Engineer – Vehicle Software Engineering Services</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfcd3234ed7c76b1</t>
+          <t>https://www.indeed.com/viewjob?jk=e1e3f3d87b0c456d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NIKSUN, Inc.</t>
+          <t>Digital Consultants</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, SQS, ECS, Azure, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,67 +2036,67 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fd5208875d3c1b2</t>
+          <t>https://www.indeed.com/viewjob?jk=d5b05b32ba6e729a</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CD&amp;A Data Engineer</t>
+          <t>Senior Development Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54bc52360158a211</t>
+          <t>https://www.indeed.com/viewjob?jk=4e32c70852b2e7e9</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer</t>
+          <t>Senior Development Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SWBC</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=075826e3e1704244</t>
+          <t>https://www.indeed.com/viewjob?jk=3f53654a42d5f44e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Engineer 2: AI Agentic Platform (Hybrid - Seattle, WA)</t>
+          <t>Senior Development Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1a42d221dac8991</t>
+          <t>https://www.indeed.com/viewjob?jk=74408bc2ca90f29e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CD&amp;A Data Engineer</t>
+          <t>Senior Development Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6cb0aa04ee83dc1</t>
+          <t>https://www.indeed.com/viewjob?jk=cfcd3234ed7c76b1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer – Python + React (Healthcare Domain)</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Nova Web Technologies</t>
+          <t>NIKSUN, Inc.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff5c44492f4137d0</t>
+          <t>https://www.indeed.com/viewjob?jk=0fd5208875d3c1b2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Production Digitalization Intern (Fall 2026)</t>
+          <t>CD&amp;A Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BMW Group</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Woodruff, SC, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, RDS, Azure, Oracle, PostgreSQL, ETL, ELT, Amazon QuickSight</t>
+          <t>RDS, Azure, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d2c3fbbbf2753ab</t>
+          <t>https://www.indeed.com/viewjob?jk=54bc52360158a211</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DBX/PowerBI Developer</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>SWBC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Cloud Storage, Spark, Scala, Snowflake, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1532e72abbad0fcf</t>
+          <t>https://www.indeed.com/viewjob?jk=075826e3e1704244</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Engineer 2: AI Agentic Platform (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Spark, Snowflake, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline, Terraform</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f417fbf524598c0</t>
+          <t>https://www.indeed.com/viewjob?jk=e1a42d221dac8991</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Azure Engineer (Associate)</t>
+          <t>CD&amp;A Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>RDS, Azure, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dbe236b626e4a53</t>
+          <t>https://www.indeed.com/viewjob?jk=f6cb0aa04ee83dc1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer (Advanced Threat Protection)</t>
+          <t>Data Engineer – Python + React (Healthcare Domain)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Nova Web Technologies</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Terraform, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2c3719c3e2ec42</t>
+          <t>https://www.indeed.com/viewjob?jk=ff5c44492f4137d0</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Associate Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CNA Insurance</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947710ea68d4354a</t>
+          <t>https://www.indeed.com/viewjob?jk=f990189dc2794b76</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>Production Digitalization Intern (Fall 2026)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Rise Collective</t>
+          <t>BMW Group</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Woodruff, SC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, NoSQL</t>
+          <t>AWS, Glue, Athena, RDS, Azure, Oracle, PostgreSQL, ETL, ELT, Amazon QuickSight</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff3b252b91a197e5</t>
+          <t>https://www.indeed.com/viewjob?jk=6d2c3fbbbf2753ab</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>DBX/PowerBI Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Cloud Storage, Spark, Scala, Snowflake, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,19 +2491,19 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be9e819ada5cf6a</t>
+          <t>https://www.indeed.com/viewjob?jk=1532e72abbad0fcf</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior SQL Developer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
+          <t>AWS, Glue, RDS, Spark, Snowflake, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b418f223555b73b9</t>
+          <t>https://www.indeed.com/viewjob?jk=1f417fbf524598c0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Azure Engineer (Associate)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
+          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707d30063b198a61</t>
+          <t>https://www.indeed.com/viewjob?jk=9dbe236b626e4a53</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SQL Platform Engineer</t>
+          <t>Sr Cloud Infrastructure Engineer (Advanced Threat Protection)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
+          <t>AWS, GCP, BigQuery, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e965a90207e77c</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2c3719c3e2ec42</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>S3, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=257bf20abcf10b52</t>
+          <t>https://www.indeed.com/viewjob?jk=aa97fcdc7f844184</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Crumbl Cookies Franchises</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60db0ac4d21d1076</t>
+          <t>https://www.indeed.com/viewjob?jk=257bf20abcf10b52</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Crumbl Cookies Franchises</t>
+          <t>CNA Insurance</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c53bb7a7aa686c9</t>
+          <t>https://www.indeed.com/viewjob?jk=947710ea68d4354a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineering Senior Advisor- Hybrid</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Crumbl Cookies Franchises</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Spark Streaming, Kafka, Oracle, MongoDB, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ab95bf144a98568</t>
+          <t>https://www.indeed.com/viewjob?jk=60db0ac4d21d1076</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineering Senior Advisor- Hybrid</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Crumbl Cookies Franchises</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Spark Streaming, Kafka, Oracle, MongoDB, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceca754c6b6fbfd5</t>
+          <t>https://www.indeed.com/viewjob?jk=4c53bb7a7aa686c9</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Software Engineering Senior Advisor- Hybrid</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, Spark Streaming, Kafka, Oracle, MongoDB, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55da546db249541e</t>
+          <t>https://www.indeed.com/viewjob?jk=1ab95bf144a98568</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer, IT Software</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Cypress, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cde05fe8d78b7bea</t>
+          <t>https://www.indeed.com/viewjob?jk=be2ef33d0192f63d</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (.NET )</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,19 +2876,19 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8fae101fea70214</t>
+          <t>https://www.indeed.com/viewjob?jk=3be9e819ada5cf6a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Blockchain Engineer</t>
+          <t>Senior SQL Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=678a055b3ce18049</t>
+          <t>https://www.indeed.com/viewjob?jk=b418f223555b73b9</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Rise Collective</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b9a027a38e2401</t>
+          <t>https://www.indeed.com/viewjob?jk=f9745f84cfd688af</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Power BI Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Hussmann</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bridgeton, MO, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=454d2924e4649642</t>
+          <t>https://www.indeed.com/viewjob?jk=55da546db249541e</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Associate Engineer, IT Software</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Spurs Sports &amp; Entertainment</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31a3c71dc92d0e0c</t>
+          <t>https://www.indeed.com/viewjob?jk=cde05fe8d78b7bea</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer, Go to Market (Remote)</t>
+          <t>Senior Software Engineer (.NET )</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27f893425f230116</t>
+          <t>https://www.indeed.com/viewjob?jk=a8fae101fea70214</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Metronet</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8988ab1d912fc2fc</t>
+          <t>https://www.indeed.com/viewjob?jk=707d30063b198a61</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>SQL Platform Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Offchain Labs</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, CodeBuild, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a00c080490fe5a6</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e965a90207e77c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2de73d2117d18151</t>
+          <t>https://www.indeed.com/viewjob?jk=18b9a027a38e2401</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Frontend Software Engineer</t>
+          <t>Sr. Power BI Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Dresser Utility Solutions</t>
+          <t>Hussmann</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Bridgeton, MO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e77c6f0d763f738</t>
+          <t>https://www.indeed.com/viewjob?jk=454d2924e4649642</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer II, Wayfair Sponsored Shops</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>Spurs Sports &amp; Entertainment</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1700b3ad8a2acabe</t>
+          <t>https://www.indeed.com/viewjob?jk=31a3c71dc92d0e0c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>Data Engineer, Go to Market (Remote)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>IQVIA</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Hive, Spark, PySpark, Scala, ETL, ELT, Terraform</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=409022a27d0ec067</t>
+          <t>https://www.indeed.com/viewjob?jk=27f893425f230116</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer - Senior Associate</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>Offchain Labs</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Hadoop, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, CodeBuild, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,67 +3296,67 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b998a3d5965b93e8</t>
+          <t>https://www.indeed.com/viewjob?jk=8a00c080490fe5a6</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Redford, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, Scala, DynamoDB, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29332168c78c58c</t>
+          <t>https://www.indeed.com/viewjob?jk=4fcfc8455bb28a5a</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d23e98febb4af71d</t>
+          <t>https://www.indeed.com/viewjob?jk=2de73d2117d18151</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Frontend Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Snooze an AM Eatery</t>
+          <t>Dresser Utility Solutions</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65eaed35b3d68901</t>
+          <t>https://www.indeed.com/viewjob?jk=2e77c6f0d763f738</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Junior Data Engineer (Faculty Specialist)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>University of Maryland University College</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>College Park, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Hive, Spark, SQL Server, PostgreSQL, Cassandra, ETL, Git</t>
+          <t>RDS, BigQuery, Dimensional Modeling, ETL, ELT, dbt, Tableau, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaedc5d1808c1ed5</t>
+          <t>https://www.indeed.com/viewjob?jk=3775c83bc5fdd8c7</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platforms &amp; Monetization</t>
+          <t>Software Engineer II, Wayfair Sponsored Shops</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Wowza Media Systems</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, MySQL, Data Modeling, ETL, REST API integration, Terraform</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa5b3c703b2170b9</t>
+          <t>https://www.indeed.com/viewjob?jk=1700b3ad8a2acabe</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
+          <t>AWS, Glue, EMR, Hive, Spark, PySpark, Scala, ETL, ELT, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35918117efc7ec73</t>
+          <t>https://www.indeed.com/viewjob?jk=409022a27d0ec067</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer - Senior Associate</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Hadoop, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=debc73a0a4d41c46</t>
+          <t>https://www.indeed.com/viewjob?jk=b998a3d5965b93e8</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Engineer, AI/ML Software</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Analog Devices</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Redford, MI, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=664a13900407cad4</t>
+          <t>https://www.indeed.com/viewjob?jk=c29332168c78c58c</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Lakebase Sales Specialist-Manufacturing</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50ab1973f17e0989</t>
+          <t>https://www.indeed.com/viewjob?jk=d23e98febb4af71d</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>Snooze an AM Eatery</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Python</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, Airflow</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ec915a33af5dd7f</t>
+          <t>https://www.indeed.com/viewjob?jk=65eaed35b3d68901</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>HR -Data Scientist</t>
+          <t>Junior Data Engineer (Faculty Specialist)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>University of Maryland University College</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>College Park, MD, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
+          <t>AWS, GCP, Hadoop, Hive, Spark, SQL Server, PostgreSQL, Cassandra, ETL, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b5d60890bd05332</t>
+          <t>https://www.indeed.com/viewjob?jk=aaedc5d1808c1ed5</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Architect 3 (Data Analyst 3)</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>University of Connecticut</t>
+          <t>The Carlyle Group</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Storrs, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,17 +3706,227 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=35918117efc7ec73</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=debc73a0a4d41c46</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Lakebase Sales Specialist-Manufacturing</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50ab1973f17e0989</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>HR -Data Scientist</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Renton, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b5d60890bd05332</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Data Architect 3 (Data Analyst 3)</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>University of Connecticut</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Storrs, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
           <t>RDS, Scala, Oracle, SQL Server, ETL, Pentaho, Power BI, Airflow, Python, SQL</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3b2f300a70f64192</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Cloud Network Engineer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>VSG Business Solutions</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Farmington Hills, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=affe8303aaf58004</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Senior Engineer, AI/ML Software</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Analog Devices</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=664a13900407cad4</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-09.xlsx
+++ b/results/job_matches_2026-06-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineering Senior Advisor- Hybrid</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>The Motley Fool</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.5</v>
+        <v>20.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, API Gateway, IAM, RDS, Databricks, Spark</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, Snowflake, clustering keys, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b55889f7ea9b40e</t>
+          <t>https://www.indeed.com/viewjob?jk=76c7190df188f528</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer Senior</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Motley Fool</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, Snowflake, clustering keys, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Sqoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76c7190df188f528</t>
+          <t>https://www.indeed.com/viewjob?jk=d18ea85c2c928c35</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer Senior</t>
+          <t>AWS Data Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>Exaways Corporation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,34 +556,34 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Sqoop, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d18ea85c2c928c35</t>
+          <t>https://www.indeed.com/viewjob?jk=bf85c1090a97cd0a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Platform</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Databricks, Unity Catalog, Spark</t>
+          <t>AWS, API Gateway, IAM, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,59 +601,59 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=257ec7c1915b24c6</t>
+          <t>https://www.indeed.com/viewjob?jk=2da5893cfc35a86b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AI Engineer - AI/ML</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Vertex AI, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2da5893cfc35a86b</t>
+          <t>https://www.indeed.com/viewjob?jk=603c741187a35795</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Engineer - AI/ML</t>
+          <t>Senior Data Engineer (Requiring GCP)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Vertex AI, Hadoop, Spark, PySpark</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=603c741187a35795</t>
+          <t>https://www.indeed.com/viewjob?jk=a9cfe57c8aa77945</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9cfe57c8aa77945</t>
+          <t>https://www.indeed.com/viewjob?jk=546ae471f5ede086</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=546ae471f5ede086</t>
+          <t>https://www.indeed.com/viewjob?jk=1c811d03d5aca192</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c811d03d5aca192</t>
+          <t>https://www.indeed.com/viewjob?jk=0b6a62dfef2d6dab</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b6a62dfef2d6dab</t>
+          <t>https://www.indeed.com/viewjob?jk=f8656393b23155db</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Requiring GCP)</t>
+          <t>AI Software Engineer, Senior</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,59 +846,59 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8656393b23155db</t>
+          <t>https://www.indeed.com/viewjob?jk=212d73dd2934b416</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Roku</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Spark, Scala, Kafka, NoSQL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, ECS, RDS, Databricks, Unity Catalog, Hive</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e2b721d35d7a5a7</t>
+          <t>https://www.indeed.com/viewjob?jk=ae38a9c283b62879</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Roku</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SNS, ECS, IAM, RDS, Scala, PostgreSQL</t>
+          <t>AWS, RDS, GCP, Spark, Scala, Kafka, NoSQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,59 +916,59 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=882f952f94db3f29</t>
+          <t>https://www.indeed.com/viewjob?jk=8e2b721d35d7a5a7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Bricks Migration and Support engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
+          <t>AWS, IAM, Azure, Data Factory, Databricks, Blob Storage, Unity Catalog, Delta Live Tables, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877524bbcd4e4f56</t>
+          <t>https://www.indeed.com/viewjob?jk=f89526bd8706b6bf</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Bricks Migration and Support engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Data Factory, Databricks, Blob Storage, Unity Catalog, Delta Live Tables, Cloud Storage, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f89526bd8706b6bf</t>
+          <t>https://www.indeed.com/viewjob?jk=7cd0ed9ff6e64aa7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cd0ed9ff6e64aa7</t>
+          <t>https://www.indeed.com/viewjob?jk=9652a3e159336480</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Capstone Logistics, LLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Peachtree Corners, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,69 +1046,69 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9652a3e159336480</t>
+          <t>https://www.indeed.com/viewjob?jk=30d85c0bd52ccea6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Distinguished Software Engineer (Big Data &amp; AI)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capstone Logistics, LLC</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Peachtree Corners, GA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30d85c0bd52ccea6</t>
+          <t>https://www.indeed.com/viewjob?jk=a981ef29c01bf602</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Distinguished Software Engineer (Big Data &amp; AI)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a981ef29c01bf602</t>
+          <t>https://www.indeed.com/viewjob?jk=4e1214688100a67a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>API Integrations Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Colorado Access</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,42 +1151,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, DynamoDB, Splunk, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Snowflake, SQL Server, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e1214688100a67a</t>
+          <t>https://www.indeed.com/viewjob?jk=3dea7c38b1b46e2c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>API Integrations Developer</t>
+          <t>Senior Data Engineer - PGIM Technology (Hybrid - Newark, NJ)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Colorado Access</t>
+          <t>PGIM</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Snowflake, SQL Server, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dea7c38b1b46e2c</t>
+          <t>https://www.indeed.com/viewjob?jk=b7feca5e666659d5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data/ML Engineer (AWS)</t>
+          <t>Senior Data Engineer, Analytics</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Capnexus</t>
+          <t>Lovevery</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, API Gateway, RDS, Azure</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb618ea44d30c0e0</t>
+          <t>https://www.indeed.com/viewjob?jk=b019f71f6d426d97</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - PGIM Technology (Hybrid - Newark, NJ)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PGIM</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7feca5e666659d5</t>
+          <t>https://www.indeed.com/viewjob?jk=34801161eca101a2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - PGIM Technology</t>
+          <t>Senior Data/Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Spark, Scala, Data Modeling, ETL, dbt, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ddb3e15556877d</t>
+          <t>https://www.indeed.com/viewjob?jk=260e9231f9bc608e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Analytics</t>
+          <t>Specialist Solutions Architect - Data Engineering</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lovevery</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,112 +1326,112 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b019f71f6d426d97</t>
+          <t>https://www.indeed.com/viewjob?jk=06eee63ec8fb01b9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Full Stack Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>L&amp;T Technology Services Ltd.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, S3, IAM, Cloud Storage, Spark, Scala, MySQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34801161eca101a2</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c4b06a84a76fe1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data/Machine Learning Engineer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Data Modeling, ETL, dbt, MLOps, CI/CD, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=260e9231f9bc608e</t>
+          <t>https://www.indeed.com/viewjob?jk=8e55aae80dce9806</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>DTN</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06eee63ec8fb01b9</t>
+          <t>https://www.indeed.com/viewjob?jk=cb35c7b57058adb4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI Full Stack Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>L&amp;T Technology Services Ltd.</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Cloud Storage, Spark, Scala, MySQL, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, BigQuery, Cloud Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c4b06a84a76fe1</t>
+          <t>https://www.indeed.com/viewjob?jk=6773c1c434a7ae57</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DTN</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb35c7b57058adb4</t>
+          <t>https://www.indeed.com/viewjob?jk=5232892f9a4a9b08</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Operations Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10ead8343cec4879</t>
+          <t>https://www.indeed.com/viewjob?jk=dd1103c64558f430</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=162c2ab9f292809c</t>
+          <t>https://www.indeed.com/viewjob?jk=8d135475bf2adc12</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Carollo Engineers, Inc.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>Azure, Synapse Analytics, Spark, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7be54a20fbf4431</t>
+          <t>https://www.indeed.com/viewjob?jk=ab80492ce8c08674</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>HealthStream</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, BigQuery, Cloud Storage, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6773c1c434a7ae57</t>
+          <t>https://www.indeed.com/viewjob?jk=c6929e10d2183d6c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Software Engineer</t>
+          <t>Sr. Engineer, Site Reliability</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Syniti</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, S3, SQS, IAM, RDS, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5232892f9a4a9b08</t>
+          <t>https://www.indeed.com/viewjob?jk=0a9aaaa695359595</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior AI Operations Engineer</t>
+          <t>Senior BI Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Soleo Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd1103c64558f430</t>
+          <t>https://www.indeed.com/viewjob?jk=dedc6497a9161a47</t>
         </is>
       </c>
     </row>
@@ -1733,20 +1733,20 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>DTN</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,199 +1756,199 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d135475bf2adc12</t>
+          <t>https://www.indeed.com/viewjob?jk=33d845a6e90fbede</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Carollo Engineers, Inc.</t>
+          <t>Verana Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Spark, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab80492ce8c08674</t>
+          <t>https://www.indeed.com/viewjob?jk=b898217d67c6bb05</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Data Engineer - GTM Team</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HealthStream</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Databricks, Delta Live Tables, Scala, Kafka, Polars, Snowflake, PostgreSQL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6929e10d2183d6c</t>
+          <t>https://www.indeed.com/viewjob?jk=71238d288bcde281</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Site Reliability</t>
+          <t>Data Engineer - GTM Team</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Syniti</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, IAM, RDS, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Databricks, Delta Live Tables, Scala, Kafka, Polars, Snowflake, PostgreSQL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a9aaaa695359595</t>
+          <t>https://www.indeed.com/viewjob?jk=97105581153651c2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior BI Data Engineer</t>
+          <t>Powertrain Embedded ASW , DevOps and Compiler Toolchain Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Soleo Health</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, ETL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dedc6497a9161a47</t>
+          <t>https://www.indeed.com/viewjob?jk=022045c10afd20b1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-Stack Software Engineer – Vehicle Software Engineering Services</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DTN</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, ELT, CI/CD</t>
+          <t>Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33d845a6e90fbede</t>
+          <t>https://www.indeed.com/viewjob?jk=e1e3f3d87b0c456d</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Powertrain Embedded ASW , DevOps and Compiler Toolchain Engineer</t>
+          <t>Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Digital Consultants</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, ETL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, SQS, ECS, Azure, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022045c10afd20b1</t>
+          <t>https://www.indeed.com/viewjob?jk=d5b05b32ba6e729a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer – Vehicle Software Engineering Services</t>
+          <t>Senior Development Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1e3f3d87b0c456d</t>
+          <t>https://www.indeed.com/viewjob?jk=4e32c70852b2e7e9</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer</t>
+          <t>Senior Development Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Digital Consultants</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, SQS, ECS, Azure, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5b05b32ba6e729a</t>
+          <t>https://www.indeed.com/viewjob?jk=3f53654a42d5f44e</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e32c70852b2e7e9</t>
+          <t>https://www.indeed.com/viewjob?jk=74408bc2ca90f29e</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f53654a42d5f44e</t>
+          <t>https://www.indeed.com/viewjob?jk=cfcd3234ed7c76b1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Development Engineer (Core Engine)</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>NIKSUN, Inc.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,67 +2141,67 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74408bc2ca90f29e</t>
+          <t>https://www.indeed.com/viewjob?jk=0fd5208875d3c1b2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Development Engineer (Core Engine)</t>
+          <t>CD&amp;A Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Azure, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfcd3234ed7c76b1</t>
+          <t>https://www.indeed.com/viewjob?jk=54bc52360158a211</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NIKSUN, Inc.</t>
+          <t>SWBC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fd5208875d3c1b2</t>
+          <t>https://www.indeed.com/viewjob?jk=075826e3e1704244</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CD&amp;A Data Engineer</t>
+          <t>Senior Engineer 2: AI Agentic Platform (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54bc52360158a211</t>
+          <t>https://www.indeed.com/viewjob?jk=e1a42d221dac8991</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer</t>
+          <t>CD&amp;A Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SWBC</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=075826e3e1704244</t>
+          <t>https://www.indeed.com/viewjob?jk=f6cb0aa04ee83dc1</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Engineer 2: AI Agentic Platform (Hybrid - Seattle, WA)</t>
+          <t>Associate Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1a42d221dac8991</t>
+          <t>https://www.indeed.com/viewjob?jk=f990189dc2794b76</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CD&amp;A Data Engineer</t>
+          <t>Production Digitalization Intern (Fall 2026)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>BMW Group</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Woodruff, SC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Azure DevOps</t>
+          <t>AWS, Glue, Athena, RDS, Azure, Oracle, PostgreSQL, ETL, ELT, Amazon QuickSight</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6cb0aa04ee83dc1</t>
+          <t>https://www.indeed.com/viewjob?jk=6d2c3fbbbf2753ab</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer – Python + React (Healthcare Domain)</t>
+          <t>DBX/PowerBI Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nova Web Technologies</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Cloud Storage, Spark, Scala, Snowflake, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff5c44492f4137d0</t>
+          <t>https://www.indeed.com/viewjob?jk=1532e72abbad0fcf</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Associate Site Reliability Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, RDS, Spark, Snowflake, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f990189dc2794b76</t>
+          <t>https://www.indeed.com/viewjob?jk=1f417fbf524598c0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Production Digitalization Intern (Fall 2026)</t>
+          <t>Azure Engineer (Associate)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BMW Group</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Woodruff, SC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, RDS, Azure, Oracle, PostgreSQL, ETL, ELT, Amazon QuickSight</t>
+          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d2c3fbbbf2753ab</t>
+          <t>https://www.indeed.com/viewjob?jk=9dbe236b626e4a53</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DBX/PowerBI Developer</t>
+          <t>Sr Cloud Infrastructure Engineer (Advanced Threat Protection)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Cloud Storage, Spark, Scala, Snowflake, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, GCP, BigQuery, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1532e72abbad0fcf</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2c3719c3e2ec42</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Spark, Snowflake, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline, Terraform</t>
+          <t>S3, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f417fbf524598c0</t>
+          <t>https://www.indeed.com/viewjob?jk=aa97fcdc7f844184</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Azure Engineer (Associate)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Crumbl Cookies Franchises</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dbe236b626e4a53</t>
+          <t>https://www.indeed.com/viewjob?jk=60db0ac4d21d1076</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer (Advanced Threat Protection)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Crumbl Cookies Franchises</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Terraform, Git</t>
+          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2c3719c3e2ec42</t>
+          <t>https://www.indeed.com/viewjob?jk=4c53bb7a7aa686c9</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>CNA Insurance</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, GitHub Actions</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa97fcdc7f844184</t>
+          <t>https://www.indeed.com/viewjob?jk=947710ea68d4354a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Cypress, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=257bf20abcf10b52</t>
+          <t>https://www.indeed.com/viewjob?jk=be2ef33d0192f63d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CNA Insurance</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947710ea68d4354a</t>
+          <t>https://www.indeed.com/viewjob?jk=3be9e819ada5cf6a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior SQL Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Crumbl Cookies Franchises</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60db0ac4d21d1076</t>
+          <t>https://www.indeed.com/viewjob?jk=b418f223555b73b9</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Crumbl Cookies Franchises</t>
+          <t>Rise Collective</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c53bb7a7aa686c9</t>
+          <t>https://www.indeed.com/viewjob?jk=f9745f84cfd688af</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineering Senior Advisor- Hybrid</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Spark Streaming, Kafka, Oracle, MongoDB, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ab95bf144a98568</t>
+          <t>https://www.indeed.com/viewjob?jk=55da546db249541e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Sr Associate Engineer, IT Software</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Cypress, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be2ef33d0192f63d</t>
+          <t>https://www.indeed.com/viewjob?jk=cde05fe8d78b7bea</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Software Engineer (.NET )</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,14 +2876,14 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be9e819ada5cf6a</t>
+          <t>https://www.indeed.com/viewjob?jk=a8fae101fea70214</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior SQL Developer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b418f223555b73b9</t>
+          <t>https://www.indeed.com/viewjob?jk=707d30063b198a61</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>SQL Platform Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Rise Collective</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9745f84cfd688af</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e965a90207e77c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55da546db249541e</t>
+          <t>https://www.indeed.com/viewjob?jk=257bf20abcf10b52</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer, IT Software</t>
+          <t>Senior Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>SportsBiz Group Inc</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,42 +3006,42 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Unity Catalog, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cde05fe8d78b7bea</t>
+          <t>https://www.indeed.com/viewjob?jk=eecd0ded4500842f</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (.NET )</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8fae101fea70214</t>
+          <t>https://www.indeed.com/viewjob?jk=18b9a027a38e2401</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Sr. Power BI Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>Hussmann</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bridgeton, MO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707d30063b198a61</t>
+          <t>https://www.indeed.com/viewjob?jk=454d2924e4649642</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SQL Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>Spurs Sports &amp; Entertainment</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e965a90207e77c</t>
+          <t>https://www.indeed.com/viewjob?jk=31a3c71dc92d0e0c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, Scala, DynamoDB, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b9a027a38e2401</t>
+          <t>https://www.indeed.com/viewjob?jk=4fcfc8455bb28a5a</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. Power BI Engineer</t>
+          <t>Frontend Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Hussmann</t>
+          <t>Dresser Utility Solutions</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bridgeton, MO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=454d2924e4649642</t>
+          <t>https://www.indeed.com/viewjob?jk=2e77c6f0d763f738</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Spurs Sports &amp; Entertainment</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,137 +3226,137 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31a3c71dc92d0e0c</t>
+          <t>https://www.indeed.com/viewjob?jk=2de73d2117d18151</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer, Go to Market (Remote)</t>
+          <t>AWS Serverless Full Stack Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Capnexus</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Scala, DynamoDB, Amazon QuickSight</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27f893425f230116</t>
+          <t>https://www.indeed.com/viewjob?jk=38feb710a36ff9f4</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Offchain Labs</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, CodeBuild, Terraform, Kubernetes</t>
+          <t>RDS, BigQuery, Dimensional Modeling, ETL, ELT, dbt, Tableau, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a00c080490fe5a6</t>
+          <t>https://www.indeed.com/viewjob?jk=3775c83bc5fdd8c7</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Software Engineer II, Wayfair Sponsored Shops</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Scala, DynamoDB, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fcfc8455bb28a5a</t>
+          <t>https://www.indeed.com/viewjob?jk=1700b3ad8a2acabe</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Hive, Spark, PySpark, Scala, ETL, ELT, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2de73d2117d18151</t>
+          <t>https://www.indeed.com/viewjob?jk=409022a27d0ec067</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Frontend Software Engineer</t>
+          <t>Data Engineer - Senior Associate</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Dresser Utility Solutions</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Hadoop, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e77c6f0d763f738</t>
+          <t>https://www.indeed.com/viewjob?jk=b998a3d5965b93e8</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Redford, MI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Dimensional Modeling, ETL, ELT, dbt, Tableau, CI/CD, Jenkins, Jenkins</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3775c83bc5fdd8c7</t>
+          <t>https://www.indeed.com/viewjob?jk=c29332168c78c58c</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer II, Wayfair Sponsored Shops</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1700b3ad8a2acabe</t>
+          <t>https://www.indeed.com/viewjob?jk=d23e98febb4af71d</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>IQVIA</t>
+          <t>Snooze an AM Eatery</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Hive, Spark, PySpark, Scala, ETL, ELT, Terraform</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, Airflow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=409022a27d0ec067</t>
+          <t>https://www.indeed.com/viewjob?jk=65eaed35b3d68901</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer - Senior Associate</t>
+          <t>Junior Data Engineer (Faculty Specialist)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>University of Maryland University College</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>College Park, MD, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Hadoop, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, GCP, Hadoop, Hive, Spark, SQL Server, PostgreSQL, Cassandra, ETL, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b998a3d5965b93e8</t>
+          <t>https://www.indeed.com/viewjob?jk=aaedc5d1808c1ed5</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>The Carlyle Group</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Redford, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29332168c78c58c</t>
+          <t>https://www.indeed.com/viewjob?jk=35918117efc7ec73</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Data Engineer- Hybrid Onsite Des Moines, Iowa</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d23e98febb4af71d</t>
+          <t>https://www.indeed.com/viewjob?jk=81029ffa4d7910b4</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Snooze an AM Eatery</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, Airflow</t>
+          <t>AWS, Azure, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65eaed35b3d68901</t>
+          <t>https://www.indeed.com/viewjob?jk=debc73a0a4d41c46</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Junior Data Engineer (Faculty Specialist)</t>
+          <t>Lakebase Sales Specialist-Manufacturing</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>University of Maryland University College</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>College Park, MD, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Hive, Spark, SQL Server, PostgreSQL, Cassandra, ETL, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaedc5d1808c1ed5</t>
+          <t>https://www.indeed.com/viewjob?jk=50ab1973f17e0989</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>HR -Data Scientist</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
+          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35918117efc7ec73</t>
+          <t>https://www.indeed.com/viewjob?jk=2b5d60890bd05332</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Architect 3 (Data Analyst 3)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>University of Connecticut</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Storrs, CT, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Scala, Oracle, SQL Server, ETL, Pentaho, Power BI, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=debc73a0a4d41c46</t>
+          <t>https://www.indeed.com/viewjob?jk=3b2f300a70f64192</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Lakebase Sales Specialist-Manufacturing</t>
+          <t>Cloud Network Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>VSG Business Solutions</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50ab1973f17e0989</t>
+          <t>https://www.indeed.com/viewjob?jk=affe8303aaf58004</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>HR -Data Scientist</t>
+          <t>Senior Engineer, AI/ML Software</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Analog Devices</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3820,111 +3820,6 @@
         </is>
       </c>
       <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2b5d60890bd05332</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Data Architect 3 (Data Analyst 3)</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>University of Connecticut</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Storrs, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Oracle, SQL Server, ETL, Pentaho, Power BI, Airflow, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3b2f300a70f64192</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Cloud Network Engineer</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>VSG Business Solutions</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Farmington Hills, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=affe8303aaf58004</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Senior Engineer, AI/ML Software</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Analog Devices</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=664a13900407cad4</t>
         </is>

--- a/results/job_matches_2026-06-09.xlsx
+++ b/results/job_matches_2026-06-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,52 +573,52 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AI Engineer - AI/ML</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Vertex AI, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2da5893cfc35a86b</t>
+          <t>https://www.indeed.com/viewjob?jk=603c741187a35795</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Engineer - AI/ML</t>
+          <t>Senior Data Engineer (Requiring GCP)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Vertex AI, Hadoop, Spark, PySpark</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=603c741187a35795</t>
+          <t>https://www.indeed.com/viewjob?jk=a9cfe57c8aa77945</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9cfe57c8aa77945</t>
+          <t>https://www.indeed.com/viewjob?jk=546ae471f5ede086</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=546ae471f5ede086</t>
+          <t>https://www.indeed.com/viewjob?jk=1c811d03d5aca192</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c811d03d5aca192</t>
+          <t>https://www.indeed.com/viewjob?jk=0b6a62dfef2d6dab</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b6a62dfef2d6dab</t>
+          <t>https://www.indeed.com/viewjob?jk=f8656393b23155db</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Requiring GCP)</t>
+          <t>AI Software Engineer, Senior</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8656393b23155db</t>
+          <t>https://www.indeed.com/viewjob?jk=212d73dd2934b416</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Software Engineer, Senior</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, ECS, RDS, Databricks, Unity Catalog, Hive</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,59 +846,59 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=212d73dd2934b416</t>
+          <t>https://www.indeed.com/viewjob?jk=ae38a9c283b62879</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Roku</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, ECS, RDS, Databricks, Unity Catalog, Hive</t>
+          <t>AWS, RDS, GCP, Spark, Scala, Kafka, NoSQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae38a9c283b62879</t>
+          <t>https://www.indeed.com/viewjob?jk=8e2b721d35d7a5a7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Roku</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,17 +906,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Spark, Scala, Kafka, NoSQL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e2b721d35d7a5a7</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c144461aa2d176</t>
         </is>
       </c>
     </row>
@@ -993,17 +993,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (AWS, Databricks)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9652a3e159336480</t>
+          <t>https://www.indeed.com/viewjob?jk=74c4df1b9aa839f0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capstone Logistics, LLC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Peachtree Corners, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,112 +1046,112 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30d85c0bd52ccea6</t>
+          <t>https://www.indeed.com/viewjob?jk=9652a3e159336480</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Distinguished Software Engineer (Big Data &amp; AI)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Capstone Logistics, LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Peachtree Corners, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a981ef29c01bf602</t>
+          <t>https://www.indeed.com/viewjob?jk=30d85c0bd52ccea6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack AI Product Engineer (DataEdge)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, DynamoDB, Splunk, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e1214688100a67a</t>
+          <t>https://www.indeed.com/viewjob?jk=caded7b3c6bfb312</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>API Integrations Developer</t>
+          <t>Full Stack AI Product Engineer (DataEdge)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Colorado Access</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Snowflake, SQL Server, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dea7c38b1b46e2c</t>
+          <t>https://www.indeed.com/viewjob?jk=b469cfbb95e6de2a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - PGIM Technology (Hybrid - Newark, NJ)</t>
+          <t>Full Stack AI Product Engineer (DataEdge)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PGIM</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,54 +1196,54 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7feca5e666659d5</t>
+          <t>https://www.indeed.com/viewjob?jk=35ffec2079d73b49</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Analytics</t>
+          <t>Full Stack AI Product Engineer (DataEdge)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lovevery</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b019f71f6d426d97</t>
+          <t>https://www.indeed.com/viewjob?jk=8dd7c29dab24b04e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack AI Product Engineer (DataEdge)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1252,81 +1252,81 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34801161eca101a2</t>
+          <t>https://www.indeed.com/viewjob?jk=c3c936d966c8b145</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data/Machine Learning Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Data Modeling, ETL, dbt, MLOps, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=260e9231f9bc608e</t>
+          <t>https://www.indeed.com/viewjob?jk=4e1214688100a67a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering</t>
+          <t>API Integrations Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Colorado Access</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Snowflake, SQL Server, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,94 +1336,94 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06eee63ec8fb01b9</t>
+          <t>https://www.indeed.com/viewjob?jk=3dea7c38b1b46e2c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI Full Stack Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>L&amp;T Technology Services Ltd.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Cloud Storage, Spark, Scala, MySQL, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c4b06a84a76fe1</t>
+          <t>https://www.indeed.com/viewjob?jk=34801161eca101a2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Senior Data/Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, RDS, Spark, Scala, Data Modeling, ETL, dbt, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e55aae80dce9806</t>
+          <t>https://www.indeed.com/viewjob?jk=260e9231f9bc608e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Full Stack Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DTN</t>
+          <t>L&amp;T Technology Services Ltd.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, S3, IAM, Cloud Storage, Spark, Scala, MySQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb35c7b57058adb4</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c4b06a84a76fe1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, BigQuery, Cloud Storage, Scala, Snowflake</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6773c1c434a7ae57</t>
+          <t>https://www.indeed.com/viewjob?jk=8e55aae80dce9806</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>DTN</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5232892f9a4a9b08</t>
+          <t>https://www.indeed.com/viewjob?jk=cb35c7b57058adb4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior AI Operations Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, BigQuery, Cloud Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd1103c64558f430</t>
+          <t>https://www.indeed.com/viewjob?jk=6773c1c434a7ae57</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Operations Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d135475bf2adc12</t>
+          <t>https://www.indeed.com/viewjob?jk=dd1103c64558f430</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Carollo Engineers, Inc.</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Spark, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab80492ce8c08674</t>
+          <t>https://www.indeed.com/viewjob?jk=8d135475bf2adc12</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>HealthStream</t>
+          <t>Carollo Engineers, Inc.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, DynamoDB, CI/CD</t>
+          <t>Azure, Synapse Analytics, Spark, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6929e10d2183d6c</t>
+          <t>https://www.indeed.com/viewjob?jk=ab80492ce8c08674</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Site Reliability</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Syniti</t>
+          <t>HealthStream</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, IAM, RDS, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a9aaaa695359595</t>
+          <t>https://www.indeed.com/viewjob?jk=c6929e10d2183d6c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior BI Data Engineer</t>
+          <t>Sr. Engineer, Site Reliability</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Soleo Health</t>
+          <t>Syniti</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, SQS, IAM, RDS, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dedc6497a9161a47</t>
+          <t>https://www.indeed.com/viewjob?jk=0a9aaaa695359595</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DTN</t>
+          <t>SBA Communications</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33d845a6e90fbede</t>
+          <t>https://www.indeed.com/viewjob?jk=2d82e34990aaa316</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full-Stack Software Engineer – Vehicle Software Engineering Services</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Verana Health</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b898217d67c6bb05</t>
+          <t>https://www.indeed.com/viewjob?jk=e1e3f3d87b0c456d</t>
         </is>
       </c>
     </row>
@@ -1903,17 +1903,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer – Vehicle Software Engineering Services</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Digital Consultants</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, SQS, ECS, Azure, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1e3f3d87b0c456d</t>
+          <t>https://www.indeed.com/viewjob?jk=d5b05b32ba6e729a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer</t>
+          <t>Senior Development Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Digital Consultants</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, SQS, ECS, Azure, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5b05b32ba6e729a</t>
+          <t>https://www.indeed.com/viewjob?jk=4e32c70852b2e7e9</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e32c70852b2e7e9</t>
+          <t>https://www.indeed.com/viewjob?jk=3f53654a42d5f44e</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f53654a42d5f44e</t>
+          <t>https://www.indeed.com/viewjob?jk=74408bc2ca90f29e</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,67 +2071,67 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74408bc2ca90f29e</t>
+          <t>https://www.indeed.com/viewjob?jk=cfcd3234ed7c76b1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Development Engineer (Core Engine)</t>
+          <t>CD&amp;A Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Azure, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfcd3234ed7c76b1</t>
+          <t>https://www.indeed.com/viewjob?jk=54bc52360158a211</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NIKSUN, Inc.</t>
+          <t>SWBC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fd5208875d3c1b2</t>
+          <t>https://www.indeed.com/viewjob?jk=075826e3e1704244</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CD&amp;A Data Engineer</t>
+          <t>Senior Engineer 2: AI Agentic Platform (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54bc52360158a211</t>
+          <t>https://www.indeed.com/viewjob?jk=e1a42d221dac8991</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer</t>
+          <t>CD&amp;A Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SWBC</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=075826e3e1704244</t>
+          <t>https://www.indeed.com/viewjob?jk=f6cb0aa04ee83dc1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Engineer 2: AI Agentic Platform (Hybrid - Seattle, WA)</t>
+          <t>Associate Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1a42d221dac8991</t>
+          <t>https://www.indeed.com/viewjob?jk=f990189dc2794b76</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CD&amp;A Data Engineer</t>
+          <t>Production Digitalization Intern (Fall 2026)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>BMW Group</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Woodruff, SC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Azure DevOps</t>
+          <t>AWS, Glue, Athena, RDS, Azure, Oracle, PostgreSQL, ETL, ELT, Amazon QuickSight</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6cb0aa04ee83dc1</t>
+          <t>https://www.indeed.com/viewjob?jk=6d2c3fbbbf2753ab</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Associate Site Reliability Engineer</t>
+          <t>DBX/PowerBI Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Cloud Storage, Spark, Scala, Snowflake, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f990189dc2794b76</t>
+          <t>https://www.indeed.com/viewjob?jk=1532e72abbad0fcf</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Production Digitalization Intern (Fall 2026)</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BMW Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Woodruff, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, RDS, Azure, Oracle, PostgreSQL, ETL, ELT, Amazon QuickSight</t>
+          <t>AWS, Glue, RDS, Spark, Snowflake, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d2c3fbbbf2753ab</t>
+          <t>https://www.indeed.com/viewjob?jk=1f417fbf524598c0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DBX/PowerBI Developer</t>
+          <t>Azure Engineer (Associate)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Cloud Storage, Spark, Scala, Snowflake, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,19 +2386,19 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1532e72abbad0fcf</t>
+          <t>https://www.indeed.com/viewjob?jk=9dbe236b626e4a53</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SportsBiz Group Inc</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Spark, Snowflake, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Unity Catalog, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f417fbf524598c0</t>
+          <t>https://www.indeed.com/viewjob?jk=eecd0ded4500842f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Azure Engineer (Associate)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>S3, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dbe236b626e4a53</t>
+          <t>https://www.indeed.com/viewjob?jk=aa97fcdc7f844184</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer (Advanced Threat Protection)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Crumbl Cookies Franchises</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Terraform, Git</t>
+          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2c3719c3e2ec42</t>
+          <t>https://www.indeed.com/viewjob?jk=60db0ac4d21d1076</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>Crumbl Cookies Franchises</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa97fcdc7f844184</t>
+          <t>https://www.indeed.com/viewjob?jk=4c53bb7a7aa686c9</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Crumbl Cookies Franchises</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Cypress, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60db0ac4d21d1076</t>
+          <t>https://www.indeed.com/viewjob?jk=be2ef33d0192f63d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Crumbl Cookies Franchises</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c53bb7a7aa686c9</t>
+          <t>https://www.indeed.com/viewjob?jk=3be9e819ada5cf6a</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Senior SQL Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CNA Insurance</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947710ea68d4354a</t>
+          <t>https://www.indeed.com/viewjob?jk=b418f223555b73b9</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Cypress, CA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be2ef33d0192f63d</t>
+          <t>https://www.indeed.com/viewjob?jk=1173e19ebe24ce7c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,14 +2701,14 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be9e819ada5cf6a</t>
+          <t>https://www.indeed.com/viewjob?jk=707d30063b198a61</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior SQL Developer</t>
+          <t>SQL Platform Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2736,67 +2736,67 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b418f223555b73b9</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e965a90207e77c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Rise Collective</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, NoSQL</t>
+          <t>AWS, S3, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9745f84cfd688af</t>
+          <t>https://www.indeed.com/viewjob?jk=fda9e03abcd1738f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Sr. Power BI Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Hussmann</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Bridgeton, MO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55da546db249541e</t>
+          <t>https://www.indeed.com/viewjob?jk=454d2924e4649642</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer, IT Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Spurs Sports &amp; Entertainment</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cde05fe8d78b7bea</t>
+          <t>https://www.indeed.com/viewjob?jk=31a3c71dc92d0e0c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (.NET )</t>
+          <t>Frontend Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Dresser Utility Solutions</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,67 +2876,67 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8fae101fea70214</t>
+          <t>https://www.indeed.com/viewjob?jk=2e77c6f0d763f738</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Business Intelligence Analyst - Harrisburg, PA</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707d30063b198a61</t>
+          <t>https://www.indeed.com/viewjob?jk=9519db94431c20fc</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SQL Platform Engineer</t>
+          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,67 +2946,67 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e965a90207e77c</t>
+          <t>https://www.indeed.com/viewjob?jk=2de73d2117d18151</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>AWS Serverless Full Stack Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Capnexus</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Scala, DynamoDB, Amazon QuickSight</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=257bf20abcf10b52</t>
+          <t>https://www.indeed.com/viewjob?jk=38feb710a36ff9f4</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Full Stack AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SportsBiz Group Inc</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Unity Catalog, Scala, ELT, CI/CD</t>
+          <t>RDS, BigQuery, Dimensional Modeling, ETL, ELT, dbt, Tableau, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eecd0ded4500842f</t>
+          <t>https://www.indeed.com/viewjob?jk=3775c83bc5fdd8c7</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Software Engineer II, Wayfair Sponsored Shops</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,67 +3051,67 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b9a027a38e2401</t>
+          <t>https://www.indeed.com/viewjob?jk=1700b3ad8a2acabe</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Power BI Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Hussmann</t>
+          <t>ARUP Laboratories</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bridgeton, MO, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Glue, Redshift, Athena, IAM, Azure, GCP, BigQuery, Scala, dbt</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=454d2924e4649642</t>
+          <t>https://www.indeed.com/viewjob?jk=86a7c255f0579591</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Senior Associate</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Spurs Sports &amp; Entertainment</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Hadoop, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,67 +3121,67 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31a3c71dc92d0e0c</t>
+          <t>https://www.indeed.com/viewjob?jk=b998a3d5965b93e8</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Redford, MI, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Scala, DynamoDB, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fcfc8455bb28a5a</t>
+          <t>https://www.indeed.com/viewjob?jk=c29332168c78c58c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Frontend Software Engineer</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Dresser Utility Solutions</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e77c6f0d763f738</t>
+          <t>https://www.indeed.com/viewjob?jk=d23e98febb4af71d</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>Snooze an AM Eatery</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, Airflow</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2de73d2117d18151</t>
+          <t>https://www.indeed.com/viewjob?jk=65eaed35b3d68901</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AWS Serverless Full Stack Engineer</t>
+          <t>Data Engineer- Hybrid Onsite Des Moines, Iowa</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Capnexus</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Scala, DynamoDB, Amazon QuickSight</t>
+          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38feb710a36ff9f4</t>
+          <t>https://www.indeed.com/viewjob?jk=81029ffa4d7910b4</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Expert Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Harris Computer</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Dimensional Modeling, ETL, ELT, dbt, Tableau, CI/CD, Jenkins, Jenkins</t>
+          <t>Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git, Datadog</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3775c83bc5fdd8c7</t>
+          <t>https://www.indeed.com/viewjob?jk=920841329b7f6367</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer II, Wayfair Sponsored Shops</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1700b3ad8a2acabe</t>
+          <t>https://www.indeed.com/viewjob?jk=debc73a0a4d41c46</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>HR -Data Scientist</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>IQVIA</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Hive, Spark, PySpark, Scala, ETL, ELT, Terraform</t>
+          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=409022a27d0ec067</t>
+          <t>https://www.indeed.com/viewjob?jk=2b5d60890bd05332</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer - Senior Associate</t>
+          <t>Cloud Network Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>VSG Business Solutions</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,437 +3391,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Hadoop, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b998a3d5965b93e8</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Ford Motor Company</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Redford, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c29332168c78c58c</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d23e98febb4af71d</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Snooze an AM Eatery</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, Airflow</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=65eaed35b3d68901</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Junior Data Engineer (Faculty Specialist)</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>University of Maryland University College</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>College Park, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, GCP, Hadoop, Hive, Spark, SQL Server, PostgreSQL, Cassandra, ETL, Git</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aaedc5d1808c1ed5</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Data &amp; AI Engineer</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>The Carlyle Group</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=35918117efc7ec73</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Data Engineer- Hybrid Onsite Des Moines, Iowa</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Des Moines, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=81029ffa4d7910b4</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Mastercard</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Arlington, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=debc73a0a4d41c46</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Lakebase Sales Specialist-Manufacturing</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=50ab1973f17e0989</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>HR -Data Scientist</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Renton, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2b5d60890bd05332</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Data Architect 3 (Data Analyst 3)</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>University of Connecticut</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Storrs, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Oracle, SQL Server, ETL, Pentaho, Power BI, Airflow, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3b2f300a70f64192</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Cloud Network Engineer</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>VSG Business Solutions</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Farmington Hills, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=affe8303aaf58004</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Senior Engineer, AI/ML Software</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Analog Devices</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=664a13900407cad4</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-09.xlsx
+++ b/results/job_matches_2026-06-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer Senior</t>
+          <t>AWS Data Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>Exaways Corporation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,42 +521,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Sqoop, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d18ea85c2c928c35</t>
+          <t>https://www.indeed.com/viewjob?jk=bf85c1090a97cd0a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AWS Data Architect</t>
+          <t>AI Engineer - AI/ML</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Exaways Corporation</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Vertex AI, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf85c1090a97cd0a</t>
+          <t>https://www.indeed.com/viewjob?jk=603c741187a35795</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Engineer - AI/ML</t>
+          <t>Senior Data Engineer (Requiring GCP)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Vertex AI, Hadoop, Spark, PySpark</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=603c741187a35795</t>
+          <t>https://www.indeed.com/viewjob?jk=a9cfe57c8aa77945</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9cfe57c8aa77945</t>
+          <t>https://www.indeed.com/viewjob?jk=546ae471f5ede086</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=546ae471f5ede086</t>
+          <t>https://www.indeed.com/viewjob?jk=1c811d03d5aca192</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c811d03d5aca192</t>
+          <t>https://www.indeed.com/viewjob?jk=0b6a62dfef2d6dab</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b6a62dfef2d6dab</t>
+          <t>https://www.indeed.com/viewjob?jk=f8656393b23155db</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Requiring GCP)</t>
+          <t>AI Software Engineer, Senior</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8656393b23155db</t>
+          <t>https://www.indeed.com/viewjob?jk=212d73dd2934b416</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Software Engineer, Senior</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, ECS, RDS, Databricks, Unity Catalog, Hive</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=212d73dd2934b416</t>
+          <t>https://www.indeed.com/viewjob?jk=ae38a9c283b62879</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>SENIOR DATA ENGINEER-REMOTE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Cdai</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, ECS, RDS, Databricks, Unity Catalog, Hive</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae38a9c283b62879</t>
+          <t>https://www.indeed.com/viewjob?jk=8d77a89c68dff947</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Roku</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,42 +871,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Spark, Scala, Kafka, NoSQL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e2b721d35d7a5a7</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c144461aa2d176</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Bricks Migration and Support engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala</t>
+          <t>AWS, IAM, Azure, Data Factory, Databricks, Blob Storage, Unity Catalog, Delta Live Tables, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c144461aa2d176</t>
+          <t>https://www.indeed.com/viewjob?jk=f89526bd8706b6bf</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Bricks Migration and Support engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Textron</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Data Factory, Databricks, Blob Storage, Unity Catalog, Delta Live Tables, Cloud Storage, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f89526bd8706b6bf</t>
+          <t>https://www.indeed.com/viewjob?jk=dd6d1c7f44e0199d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior Data Engineer (AWS, Databricks)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cd0ed9ff6e64aa7</t>
+          <t>https://www.indeed.com/viewjob?jk=74c4df1b9aa839f0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, Databricks)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74c4df1b9aa839f0</t>
+          <t>https://www.indeed.com/viewjob?jk=9652a3e159336480</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Capstone Logistics, LLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Peachtree Corners, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,77 +1046,77 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9652a3e159336480</t>
+          <t>https://www.indeed.com/viewjob?jk=30d85c0bd52ccea6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capstone Logistics, LLC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Peachtree Corners, GA, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30d85c0bd52ccea6</t>
+          <t>https://www.indeed.com/viewjob?jk=4e1214688100a67a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Full Stack AI Product Engineer (DataEdge)</t>
+          <t>API Integrations Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Colorado Access</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Snowflake, SQL Server, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caded7b3c6bfb312</t>
+          <t>https://www.indeed.com/viewjob?jk=3dea7c38b1b46e2c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Full Stack AI Product Engineer (DataEdge)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b469cfbb95e6de2a</t>
+          <t>https://www.indeed.com/viewjob?jk=34801161eca101a2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Full Stack AI Product Engineer (DataEdge)</t>
+          <t>Senior Data/Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Spark, Scala, Data Modeling, ETL, dbt, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,137 +1196,137 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35ffec2079d73b49</t>
+          <t>https://www.indeed.com/viewjob?jk=260e9231f9bc608e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Full Stack AI Product Engineer (DataEdge)</t>
+          <t>Sr Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Snowflake, MySQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dd7c29dab24b04e</t>
+          <t>https://www.indeed.com/viewjob?jk=3567b4ad9115c5bb</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Full Stack AI Product Engineer (DataEdge)</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3c936d966c8b145</t>
+          <t>https://www.indeed.com/viewjob?jk=8e55aae80dce9806</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>DTN</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, DynamoDB, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e1214688100a67a</t>
+          <t>https://www.indeed.com/viewjob?jk=cb35c7b57058adb4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>API Integrations Developer</t>
+          <t>Senior AI Operations Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Colorado Access</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Snowflake, SQL Server, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,137 +1336,137 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dea7c38b1b46e2c</t>
+          <t>https://www.indeed.com/viewjob?jk=dd1103c64558f430</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>HealthStream</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34801161eca101a2</t>
+          <t>https://www.indeed.com/viewjob?jk=c6929e10d2183d6c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data/Machine Learning Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Medisolv Inc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Clarksville, TN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Data Modeling, ETL, dbt, MLOps, CI/CD, Docker</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=260e9231f9bc608e</t>
+          <t>https://www.indeed.com/viewjob?jk=535ccfe8a6691562</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI Full Stack Engineer</t>
+          <t>Sr. Engineer, Site Reliability</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>L&amp;T Technology Services Ltd.</t>
+          <t>Syniti</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Cloud Storage, Spark, Scala, MySQL, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, SQS, IAM, RDS, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c4b06a84a76fe1</t>
+          <t>https://www.indeed.com/viewjob?jk=0a9aaaa695359595</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>SBA Communications</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,89 +1476,89 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e55aae80dce9806</t>
+          <t>https://www.indeed.com/viewjob?jk=2d82e34990aaa316</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Web Full Stack Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DTN</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Hagerstown, MD, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, Data Modeling, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb35c7b57058adb4</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5c8643ddfaf00e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior, Software Engineer - Web/OL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, BigQuery, Cloud Storage, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6773c1c434a7ae57</t>
+          <t>https://www.indeed.com/viewjob?jk=91781f5b6a2f9315</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior AI Operations Engineer</t>
+          <t>Full-Stack Software Engineer – Vehicle Software Engineering Services</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1567,151 +1567,151 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd1103c64558f430</t>
+          <t>https://www.indeed.com/viewjob?jk=e1e3f3d87b0c456d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - GTM Team</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, Databricks, Delta Live Tables, Scala, Kafka, Polars, Snowflake, PostgreSQL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d135475bf2adc12</t>
+          <t>https://www.indeed.com/viewjob?jk=71238d288bcde281</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Data Engineer - GTM Team</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Carollo Engineers, Inc.</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Spark, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Databricks, Delta Live Tables, Scala, Kafka, Polars, Snowflake, PostgreSQL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab80492ce8c08674</t>
+          <t>https://www.indeed.com/viewjob?jk=97105581153651c2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Powertrain Embedded ASW , DevOps and Compiler Toolchain Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HealthStream</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, ETL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6929e10d2183d6c</t>
+          <t>https://www.indeed.com/viewjob?jk=022045c10afd20b1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Site Reliability</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Syniti</t>
+          <t>Digital Consultants</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, IAM, RDS, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, SQS, ECS, Azure, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a9aaaa695359595</t>
+          <t>https://www.indeed.com/viewjob?jk=d5b05b32ba6e729a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Senior Development Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SBA Communications</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d82e34990aaa316</t>
+          <t>https://www.indeed.com/viewjob?jk=4e32c70852b2e7e9</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer – Vehicle Software Engineering Services</t>
+          <t>Senior Development Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1e3f3d87b0c456d</t>
+          <t>https://www.indeed.com/viewjob?jk=3f53654a42d5f44e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer - GTM Team</t>
+          <t>Senior Development Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Delta Live Tables, Scala, Kafka, Polars, Snowflake, PostgreSQL, ELT, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71238d288bcde281</t>
+          <t>https://www.indeed.com/viewjob?jk=74408bc2ca90f29e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer - GTM Team</t>
+          <t>Senior Development Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,42 +1851,42 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Delta Live Tables, Scala, Kafka, Polars, Snowflake, PostgreSQL, ELT, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97105581153651c2</t>
+          <t>https://www.indeed.com/viewjob?jk=cfcd3234ed7c76b1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Powertrain Embedded ASW , DevOps and Compiler Toolchain Engineer</t>
+          <t>CD&amp;A Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, ETL, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Azure, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022045c10afd20b1</t>
+          <t>https://www.indeed.com/viewjob?jk=54bc52360158a211</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Digital Consultants</t>
+          <t>SWBC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, SQS, ECS, Azure, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5b05b32ba6e729a</t>
+          <t>https://www.indeed.com/viewjob?jk=075826e3e1704244</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Development Engineer (Core Engine)</t>
+          <t>Senior Engineer 2: AI Agentic Platform (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e32c70852b2e7e9</t>
+          <t>https://www.indeed.com/viewjob?jk=e1a42d221dac8991</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Development Engineer (Core Engine)</t>
+          <t>CD&amp;A Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Azure, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,94 +2001,94 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f53654a42d5f44e</t>
+          <t>https://www.indeed.com/viewjob?jk=f6cb0aa04ee83dc1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Development Engineer (Core Engine)</t>
+          <t>Mongo Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>Spark, Snowflake, Time Travel, Oracle, SQL Server, PostgreSQL, MongoDB, DynamoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74408bc2ca90f29e</t>
+          <t>https://www.indeed.com/viewjob?jk=04eada00b787baf8</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Development Engineer (Core Engine)</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>PineCone</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Kafka, Snowflake, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfcd3234ed7c76b1</t>
+          <t>https://www.indeed.com/viewjob?jk=fb6aa5155c88f566</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CD&amp;A Data Engineer</t>
+          <t>Associate Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Azure DevOps</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54bc52360158a211</t>
+          <t>https://www.indeed.com/viewjob?jk=f990189dc2794b76</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer</t>
+          <t>Production Digitalization Intern (Fall 2026)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SWBC</t>
+          <t>BMW Group</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Woodruff, SC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Athena, RDS, Azure, Oracle, PostgreSQL, ETL, ELT, Amazon QuickSight</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=075826e3e1704244</t>
+          <t>https://www.indeed.com/viewjob?jk=6d2c3fbbbf2753ab</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Engineer 2: AI Agentic Platform (Hybrid - Seattle, WA)</t>
+          <t>DBX/PowerBI Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Cloud Storage, Spark, Scala, Snowflake, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1a42d221dac8991</t>
+          <t>https://www.indeed.com/viewjob?jk=1532e72abbad0fcf</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CD&amp;A Data Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Azure DevOps</t>
+          <t>AWS, Glue, RDS, Spark, Snowflake, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6cb0aa04ee83dc1</t>
+          <t>https://www.indeed.com/viewjob?jk=1f417fbf524598c0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Associate Site Reliability Engineer</t>
+          <t>Senior Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Unity Catalog, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f990189dc2794b76</t>
+          <t>https://www.indeed.com/viewjob?jk=eecd0ded4500842f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Production Digitalization Intern (Fall 2026)</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BMW Group</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Woodruff, SC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, RDS, Azure, Oracle, PostgreSQL, ETL, ELT, Amazon QuickSight</t>
+          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d2c3fbbbf2753ab</t>
+          <t>https://www.indeed.com/viewjob?jk=70f560ecbc79fa34</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DBX/PowerBI Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Cloud Storage, Spark, Scala, Snowflake, Dimensional Modeling, Snowflake Schema</t>
+          <t>S3, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1532e72abbad0fcf</t>
+          <t>https://www.indeed.com/viewjob?jk=aa97fcdc7f844184</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Spark, Snowflake, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f417fbf524598c0</t>
+          <t>https://www.indeed.com/viewjob?jk=1173e19ebe24ce7c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Azure Engineer (Associate)</t>
+          <t>Senior SQL Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,19 +2386,19 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dbe236b626e4a53</t>
+          <t>https://www.indeed.com/viewjob?jk=b418f223555b73b9</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Full Stack AI Engineer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SportsBiz Group Inc</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Unity Catalog, Scala, ELT, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eecd0ded4500842f</t>
+          <t>https://www.indeed.com/viewjob?jk=707d30063b198a61</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>SQL Platform Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa97fcdc7f844184</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e965a90207e77c</t>
         </is>
       </c>
     </row>
@@ -2603,17 +2603,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior SQL Developer</t>
+          <t>Solutions Architect, Customer Success - US (Remote)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>Fiddler AI</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
+          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b418f223555b73b9</t>
+          <t>https://www.indeed.com/viewjob?jk=5e29186d332dfa69</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1173e19ebe24ce7c</t>
+          <t>https://www.indeed.com/viewjob?jk=e5abed50f2367d51</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Data Engineer, Supply Chain</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,52 +2691,52 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Scala, PostgreSQL, ETL, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707d30063b198a61</t>
+          <t>https://www.indeed.com/viewjob?jk=216432e17bbf1a19</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SQL Platform Engineer</t>
+          <t>Sr Software Development Engineer - Core Platform Integration</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT, dbt</t>
+          <t>AWS, Glue, IAM, RDS, GCP, ELT, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e965a90207e77c</t>
+          <t>https://www.indeed.com/viewjob?jk=66f1bbfba1ba3212</t>
         </is>
       </c>
     </row>
@@ -2848,17 +2848,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Frontend Software Engineer</t>
+          <t>Business Intelligence Analyst - Harrisburg, PA</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Dresser Utility Solutions</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e77c6f0d763f738</t>
+          <t>https://www.indeed.com/viewjob?jk=9519db94431c20fc</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst - Harrisburg, PA</t>
+          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9519db94431c20fc</t>
+          <t>https://www.indeed.com/viewjob?jk=2de73d2117d18151</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
+          <t>Frontend Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>Dresser Utility Solutions</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2de73d2117d18151</t>
+          <t>https://www.indeed.com/viewjob?jk=2e77c6f0d763f738</t>
         </is>
       </c>
     </row>
@@ -3058,17 +3058,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ARUP Laboratories</t>
+          <t>Mazzella Companies</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, IAM, Azure, GCP, BigQuery, Scala, dbt</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86a7c255f0579591</t>
+          <t>https://www.indeed.com/viewjob?jk=90fd8da4ec416c70</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer - Senior Associate</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>Mazzella Companies</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Hadoop, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b998a3d5965b93e8</t>
+          <t>https://www.indeed.com/viewjob?jk=f3a5d0fafb158752</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Customer Data Platform Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Signet Jewelers</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Redford, MI, US USA</t>
+          <t>Coppell, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, S3, IAM, Azure, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29332168c78c58c</t>
+          <t>https://www.indeed.com/viewjob?jk=a6303a5693fb08b9</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>ARUP Laboratories</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, Glue, Redshift, Athena, IAM, Azure, GCP, BigQuery, Scala, dbt</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d23e98febb4af71d</t>
+          <t>https://www.indeed.com/viewjob?jk=86a7c255f0579591</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Senior Associate</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Snooze an AM Eatery</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Hadoop, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65eaed35b3d68901</t>
+          <t>https://www.indeed.com/viewjob?jk=b998a3d5965b93e8</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer- Hybrid Onsite Des Moines, Iowa</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Redford, MI, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81029ffa4d7910b4</t>
+          <t>https://www.indeed.com/viewjob?jk=c29332168c78c58c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Expert Site Reliability Engineer</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Harris Computer</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git, Datadog</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=920841329b7f6367</t>
+          <t>https://www.indeed.com/viewjob?jk=d23e98febb4af71d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Resiliency and Recovery Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=debc73a0a4d41c46</t>
+          <t>https://www.indeed.com/viewjob?jk=3f30acbe9dfb62b5</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>HR -Data Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
+          <t>AWS, Azure, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b5d60890bd05332</t>
+          <t>https://www.indeed.com/viewjob?jk=debc73a0a4d41c46</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Cloud Network Engineer</t>
+          <t>HR -Data Scientist</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>VSG Business Solutions</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,15 +3391,85 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
+          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b5d60890bd05332</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Data Engineer- Hybrid Onsite Des Moines, Iowa</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81029ffa4d7910b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Cloud Network Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>VSG Business Solutions</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Farmington Hills, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
           <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=affe8303aaf58004</t>
         </is>
